--- a/data/trans_orig/P40-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/P40-Habitat-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según su salud autopercibida en los últimos 12 meses en 2007</t>
+          <t>Población según su salud autopercibida en los últimos 12 meses en 2007 (tasa de respuesta: 99,92%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -738,7 +738,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>5396</t>
+          <t>4686</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -753,7 +753,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>0,78%</t>
+          <t>0,68%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>2670</t>
+          <t>2289</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>13023</t>
+          <t>12931</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0,39%</t>
+          <t>0,33%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>1,89%</t>
+          <t>1,88%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>2962</t>
+          <t>3134</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>14535</t>
+          <t>14144</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,21%</t>
+          <t>0,23%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>1,05%</t>
+          <t>1,02%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>12379</t>
+          <t>12238</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>29368</t>
+          <t>30251</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>1,78%</t>
+          <t>1,76%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>4,23%</t>
+          <t>4,36%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>40195</t>
+          <t>40525</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>68196</t>
+          <t>67645</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>5,84%</t>
+          <t>5,89%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>9,91%</t>
+          <t>9,83%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>57256</t>
+          <t>57694</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>91058</t>
+          <t>90452</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>4,14%</t>
+          <t>4,17%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>6,59%</t>
+          <t>6,54%</t>
         </is>
       </c>
     </row>
@@ -959,12 +959,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>84215</t>
+          <t>84346</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>120458</t>
+          <t>121850</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -974,12 +974,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>12,13%</t>
+          <t>12,15%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>17,36%</t>
+          <t>17,56%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -994,12 +994,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>114038</t>
+          <t>112422</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>154226</t>
+          <t>155602</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1009,12 +1009,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>16,57%</t>
+          <t>16,33%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>22,41%</t>
+          <t>22,61%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1029,12 +1029,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>206904</t>
+          <t>207817</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>261073</t>
+          <t>264727</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1044,12 +1044,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>14,97%</t>
+          <t>15,03%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>18,89%</t>
+          <t>19,15%</t>
         </is>
       </c>
     </row>
@@ -1072,12 +1072,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>424703</t>
+          <t>423515</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>475116</t>
+          <t>474253</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1087,12 +1087,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>61,2%</t>
+          <t>61,02%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>68,46%</t>
+          <t>68,33%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1107,12 +1107,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>381216</t>
+          <t>380164</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>431856</t>
+          <t>432535</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1122,12 +1122,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>55,38%</t>
+          <t>55,23%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>62,74%</t>
+          <t>62,84%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1142,12 +1142,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>824242</t>
+          <t>820661</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>891808</t>
+          <t>891125</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1157,12 +1157,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>59,63%</t>
+          <t>59,37%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>64,51%</t>
+          <t>64,46%</t>
         </is>
       </c>
     </row>
@@ -1185,12 +1185,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>102104</t>
+          <t>102528</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>141699</t>
+          <t>143638</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1200,12 +1200,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>14,71%</t>
+          <t>14,77%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>20,42%</t>
+          <t>20,7%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1220,12 +1220,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>72063</t>
+          <t>73474</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>106879</t>
+          <t>108568</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1235,12 +1235,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>10,47%</t>
+          <t>10,67%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>15,53%</t>
+          <t>15,77%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1255,12 +1255,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>185966</t>
+          <t>186097</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>242147</t>
+          <t>241274</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1270,12 +1270,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>13,45%</t>
+          <t>13,46%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>17,52%</t>
+          <t>17,45%</t>
         </is>
       </c>
     </row>
@@ -1420,7 +1420,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>9022</t>
+          <t>8960</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1435,7 +1435,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>0,94%</t>
+          <t>0,93%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1455,7 +1455,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>6708</t>
+          <t>6469</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1470,7 +1470,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>0,69%</t>
+          <t>0,67%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1485,12 +1485,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>1149</t>
+          <t>1155</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>11695</t>
+          <t>12331</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1505,7 +1505,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>0,61%</t>
+          <t>0,64%</t>
         </is>
       </c>
     </row>
@@ -1528,12 +1528,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>13790</t>
+          <t>13217</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>31850</t>
+          <t>32126</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1543,12 +1543,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>1,44%</t>
+          <t>1,38%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>3,31%</t>
+          <t>3,34%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1563,12 +1563,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>32731</t>
+          <t>33795</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>59933</t>
+          <t>60714</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1578,12 +1578,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>3,38%</t>
+          <t>3,49%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>6,19%</t>
+          <t>6,27%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1598,12 +1598,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>51683</t>
+          <t>51257</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>82763</t>
+          <t>84679</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1613,12 +1613,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>2,68%</t>
+          <t>2,66%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>4,29%</t>
+          <t>4,39%</t>
         </is>
       </c>
     </row>
@@ -1641,12 +1641,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>104893</t>
+          <t>105168</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>146614</t>
+          <t>147206</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1656,12 +1656,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>10,92%</t>
+          <t>10,95%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>15,26%</t>
+          <t>15,32%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1676,12 +1676,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>240918</t>
+          <t>238432</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>297632</t>
+          <t>295286</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1691,12 +1691,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>24,88%</t>
+          <t>24,62%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>30,73%</t>
+          <t>30,49%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1711,12 +1711,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>357421</t>
+          <t>358519</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>429054</t>
+          <t>430178</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1726,12 +1726,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>18,53%</t>
+          <t>18,58%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>22,24%</t>
+          <t>22,3%</t>
         </is>
       </c>
     </row>
@@ -1754,12 +1754,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>582813</t>
+          <t>587565</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>646683</t>
+          <t>648416</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1769,12 +1769,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>60,66%</t>
+          <t>61,15%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>67,31%</t>
+          <t>67,49%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1789,12 +1789,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>506534</t>
+          <t>503107</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>569969</t>
+          <t>569340</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1804,12 +1804,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>52,31%</t>
+          <t>51,95%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>58,86%</t>
+          <t>58,79%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1824,12 +1824,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1107761</t>
+          <t>1112556</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>1197304</t>
+          <t>1195490</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1839,12 +1839,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>57,42%</t>
+          <t>57,67%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>62,06%</t>
+          <t>61,97%</t>
         </is>
       </c>
     </row>
@@ -1867,12 +1867,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>171093</t>
+          <t>169881</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>226432</t>
+          <t>222990</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1882,12 +1882,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>17,81%</t>
+          <t>17,68%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>23,57%</t>
+          <t>23,21%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1902,12 +1902,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>95967</t>
+          <t>97198</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>138096</t>
+          <t>139098</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1917,12 +1917,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>9,91%</t>
+          <t>10,04%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>14,26%</t>
+          <t>14,36%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1937,12 +1937,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>280237</t>
+          <t>280121</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>345902</t>
+          <t>346001</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1952,7 +1952,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>14,53%</t>
+          <t>14,52%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -2102,7 +2102,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>5688</t>
+          <t>6130</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2117,7 +2117,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>0,84%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2132,12 +2132,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>981</t>
+          <t>956</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>11594</t>
+          <t>10726</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2152,7 +2152,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>1,7%</t>
+          <t>1,57%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2167,12 +2167,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>2551</t>
+          <t>2626</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>13621</t>
+          <t>14096</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2187,7 +2187,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>1,04%</t>
         </is>
       </c>
     </row>
@@ -2210,12 +2210,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>4688</t>
+          <t>4632</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>19425</t>
+          <t>19034</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2225,12 +2225,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0,69%</t>
+          <t>0,68%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>2,87%</t>
+          <t>2,81%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2245,12 +2245,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>18299</t>
+          <t>18868</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>40057</t>
+          <t>39934</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2260,12 +2260,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>2,68%</t>
+          <t>2,77%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>5,87%</t>
+          <t>5,85%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2280,12 +2280,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>26992</t>
+          <t>27234</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>51387</t>
+          <t>52950</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2295,12 +2295,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>1,99%</t>
+          <t>2,0%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>3,78%</t>
+          <t>3,89%</t>
         </is>
       </c>
     </row>
@@ -2323,12 +2323,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>72588</t>
+          <t>74397</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>109360</t>
+          <t>109232</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2338,12 +2338,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>10,71%</t>
+          <t>10,98%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>16,14%</t>
+          <t>16,12%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2358,12 +2358,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>115626</t>
+          <t>115034</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>156137</t>
+          <t>157181</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2373,12 +2373,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>16,95%</t>
+          <t>16,87%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>22,89%</t>
+          <t>23,05%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2393,12 +2393,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>198730</t>
+          <t>200368</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>252191</t>
+          <t>253113</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2408,12 +2408,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>14,62%</t>
+          <t>14,74%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>18,55%</t>
+          <t>18,62%</t>
         </is>
       </c>
     </row>
@@ -2436,12 +2436,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>418223</t>
+          <t>415669</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>469795</t>
+          <t>466456</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2451,12 +2451,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>61,72%</t>
+          <t>61,35%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>69,34%</t>
+          <t>68,84%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2471,12 +2471,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>397439</t>
+          <t>394096</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>445774</t>
+          <t>444556</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2486,12 +2486,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>58,27%</t>
+          <t>57,78%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>65,36%</t>
+          <t>65,18%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2506,12 +2506,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>831476</t>
+          <t>827871</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>900337</t>
+          <t>899136</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2521,12 +2521,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>61,16%</t>
+          <t>60,89%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>66,22%</t>
+          <t>66,13%</t>
         </is>
       </c>
     </row>
@@ -2549,12 +2549,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>110432</t>
+          <t>112094</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>153540</t>
+          <t>154385</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2564,12 +2564,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>16,3%</t>
+          <t>16,54%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>22,66%</t>
+          <t>22,79%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2584,12 +2584,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>78376</t>
+          <t>76288</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>112599</t>
+          <t>112959</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2599,12 +2599,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>11,49%</t>
+          <t>11,19%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>16,51%</t>
+          <t>16,56%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2619,12 +2619,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>197247</t>
+          <t>198910</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>251650</t>
+          <t>254044</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2634,12 +2634,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>14,51%</t>
+          <t>14,63%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>18,51%</t>
+          <t>18,68%</t>
         </is>
       </c>
     </row>
@@ -2784,7 +2784,7 @@
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>5245</t>
+          <t>6075</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2799,7 +2799,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>0,56%</t>
+          <t>0,65%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2814,12 +2814,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>3091</t>
+          <t>2977</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>14307</t>
+          <t>13992</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2829,12 +2829,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,29%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>1,38%</t>
+          <t>1,35%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2849,12 +2849,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>4108</t>
+          <t>3859</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>16489</t>
+          <t>15987</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2864,12 +2864,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>0,21%</t>
+          <t>0,19%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>0,83%</t>
+          <t>0,81%</t>
         </is>
       </c>
     </row>
@@ -2892,12 +2892,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>11840</t>
+          <t>11176</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>27417</t>
+          <t>27073</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2907,12 +2907,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>1,26%</t>
+          <t>1,19%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>2,91%</t>
+          <t>2,88%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2927,12 +2927,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>36977</t>
+          <t>36905</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>63980</t>
+          <t>64848</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2942,12 +2942,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>3,56%</t>
+          <t>3,55%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>6,16%</t>
+          <t>6,24%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2962,12 +2962,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>52869</t>
+          <t>52565</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>84265</t>
+          <t>81987</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2977,12 +2977,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>2,67%</t>
+          <t>2,65%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>4,26%</t>
+          <t>4,14%</t>
         </is>
       </c>
     </row>
@@ -3005,12 +3005,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>110030</t>
+          <t>110621</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>151688</t>
+          <t>151735</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3020,12 +3020,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>11,69%</t>
+          <t>11,75%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>16,11%</t>
+          <t>16,12%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3040,12 +3040,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>205882</t>
+          <t>204675</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>263154</t>
+          <t>261133</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3055,12 +3055,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>19,82%</t>
+          <t>19,71%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>25,34%</t>
+          <t>25,14%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3075,12 +3075,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>332493</t>
+          <t>329352</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>399221</t>
+          <t>396946</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3090,12 +3090,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>16,79%</t>
+          <t>16,63%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>20,16%</t>
+          <t>20,05%</t>
         </is>
       </c>
     </row>
@@ -3118,12 +3118,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>565237</t>
+          <t>562687</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>621056</t>
+          <t>621449</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3133,12 +3133,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>60,05%</t>
+          <t>59,78%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>65,98%</t>
+          <t>66,02%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3153,12 +3153,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>536322</t>
+          <t>542397</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>603453</t>
+          <t>604605</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3168,12 +3168,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>51,64%</t>
+          <t>52,22%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>58,1%</t>
+          <t>58,21%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3188,12 +3188,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>1119020</t>
+          <t>1121694</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>1209524</t>
+          <t>1212143</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3203,12 +3203,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>56,52%</t>
+          <t>56,65%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>61,09%</t>
+          <t>61,22%</t>
         </is>
       </c>
     </row>
@@ -3231,12 +3231,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>175348</t>
+          <t>175074</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>224212</t>
+          <t>223496</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3246,12 +3246,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>18,63%</t>
+          <t>18,6%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>23,82%</t>
+          <t>23,74%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3266,12 +3266,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>155034</t>
+          <t>154591</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>203356</t>
+          <t>203802</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3281,12 +3281,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>14,93%</t>
+          <t>14,88%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>19,58%</t>
+          <t>19,62%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3301,12 +3301,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>340743</t>
+          <t>338651</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>409712</t>
+          <t>410573</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3316,12 +3316,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>17,21%</t>
+          <t>17,1%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>20,69%</t>
+          <t>20,74%</t>
         </is>
       </c>
     </row>
@@ -3461,12 +3461,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>3372</t>
+          <t>2832</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>14866</t>
+          <t>14841</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3476,7 +3476,7 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>0,1%</t>
+          <t>0,09%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
@@ -3496,12 +3496,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>12996</t>
+          <t>12274</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>30470</t>
+          <t>31298</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3511,12 +3511,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>0,38%</t>
+          <t>0,36%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>0,93%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3531,12 +3531,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>17908</t>
+          <t>18369</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>39702</t>
+          <t>38536</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3546,12 +3546,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>0,27%</t>
+          <t>0,28%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,58%</t>
         </is>
       </c>
     </row>
@@ -3574,12 +3574,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>54687</t>
+          <t>55172</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>86899</t>
+          <t>87185</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3589,12 +3589,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>1,67%</t>
+          <t>1,69%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>2,65%</t>
+          <t>2,66%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3609,12 +3609,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>149609</t>
+          <t>150267</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>199997</t>
+          <t>201652</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3624,12 +3624,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>4,43%</t>
+          <t>4,45%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>5,92%</t>
+          <t>5,97%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3644,12 +3644,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>214592</t>
+          <t>213008</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>275655</t>
+          <t>276857</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3659,12 +3659,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>3,23%</t>
+          <t>3,2%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>4,14%</t>
+          <t>4,16%</t>
         </is>
       </c>
     </row>
@@ -3687,12 +3687,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>410043</t>
+          <t>408310</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>488261</t>
+          <t>486530</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3702,12 +3702,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>12,53%</t>
+          <t>12,47%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>14,91%</t>
+          <t>14,86%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3722,12 +3722,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>719001</t>
+          <t>719836</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>814961</t>
+          <t>818788</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3737,12 +3737,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>21,29%</t>
+          <t>21,31%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>24,13%</t>
+          <t>24,24%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3757,12 +3757,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>1149963</t>
+          <t>1158393</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>1275227</t>
+          <t>1276432</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3772,12 +3772,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>17,29%</t>
+          <t>17,42%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>19,17%</t>
+          <t>19,19%</t>
         </is>
       </c>
     </row>
@@ -3800,12 +3800,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>2054545</t>
+          <t>2048100</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>2159451</t>
+          <t>2157650</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -3815,12 +3815,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>62,76%</t>
+          <t>62,56%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>65,96%</t>
+          <t>65,91%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -3835,12 +3835,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>1877108</t>
+          <t>1876910</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>2001753</t>
+          <t>1993177</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -3850,12 +3850,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>55,58%</t>
+          <t>55,57%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>59,27%</t>
+          <t>59,01%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3870,12 +3870,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>3973038</t>
+          <t>3967181</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>4126198</t>
+          <t>4121434</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -3885,12 +3885,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>59,73%</t>
+          <t>59,65%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>62,04%</t>
+          <t>61,97%</t>
         </is>
       </c>
     </row>
@@ -3913,12 +3913,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>600371</t>
+          <t>600617</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>689622</t>
+          <t>698092</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -3928,12 +3928,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>18,34%</t>
+          <t>18,35%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>21,07%</t>
+          <t>21,32%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3948,12 +3948,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>436528</t>
+          <t>438108</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>521404</t>
+          <t>520091</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -3963,12 +3963,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>12,92%</t>
+          <t>12,97%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>15,44%</t>
+          <t>15,4%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3983,12 +3983,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>1061569</t>
+          <t>1066689</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>1181446</t>
+          <t>1187120</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -3998,12 +3998,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>15,96%</t>
+          <t>16,04%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>17,76%</t>
+          <t>17,85%</t>
         </is>
       </c>
     </row>
@@ -4180,7 +4180,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según su salud autopercibida en los últimos 12 meses en 2012</t>
+          <t>Población según su salud autopercibida en los últimos 12 meses en 2012 (tasa de respuesta: 98,99%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -4380,7 +4380,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>6512</t>
+          <t>7561</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4395,7 +4395,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>0,93%</t>
+          <t>1,08%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4410,12 +4410,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>1924</t>
+          <t>1938</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>11990</t>
+          <t>10931</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4430,7 +4430,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>1,73%</t>
+          <t>1,58%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4445,12 +4445,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>3058</t>
+          <t>3070</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>14465</t>
+          <t>14082</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4465,7 +4465,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>1,04%</t>
+          <t>1,01%</t>
         </is>
       </c>
     </row>
@@ -4488,12 +4488,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>11529</t>
+          <t>11355</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>28577</t>
+          <t>29266</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4503,12 +4503,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>1,65%</t>
+          <t>1,63%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>4,1%</t>
+          <t>4,19%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4523,12 +4523,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>27140</t>
+          <t>27218</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>51146</t>
+          <t>50405</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4538,12 +4538,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>3,92%</t>
+          <t>3,93%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>7,38%</t>
+          <t>7,27%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4558,12 +4558,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>42352</t>
+          <t>42703</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>72448</t>
+          <t>71643</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4573,12 +4573,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>3,05%</t>
+          <t>3,07%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>5,21%</t>
+          <t>5,15%</t>
         </is>
       </c>
     </row>
@@ -4601,12 +4601,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>90601</t>
+          <t>90754</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>130858</t>
+          <t>129352</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -4616,12 +4616,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>12,98%</t>
+          <t>13,01%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>18,75%</t>
+          <t>18,54%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -4636,12 +4636,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>128180</t>
+          <t>128203</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>172396</t>
+          <t>171166</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -4656,7 +4656,7 @@
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>24,88%</t>
+          <t>24,7%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -4671,12 +4671,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>228261</t>
+          <t>229764</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>288270</t>
+          <t>287479</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -4686,12 +4686,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>16,41%</t>
+          <t>16,52%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>20,73%</t>
+          <t>20,67%</t>
         </is>
       </c>
     </row>
@@ -4714,12 +4714,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>386643</t>
+          <t>387818</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>440733</t>
+          <t>439552</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4729,12 +4729,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>55,41%</t>
+          <t>55,58%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>63,16%</t>
+          <t>62,99%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4749,12 +4749,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>376221</t>
+          <t>379466</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>430171</t>
+          <t>431235</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4764,12 +4764,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>54,3%</t>
+          <t>54,77%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>62,08%</t>
+          <t>62,24%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4784,12 +4784,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>779309</t>
+          <t>782301</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>853256</t>
+          <t>855831</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4799,12 +4799,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>56,04%</t>
+          <t>56,25%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>61,36%</t>
+          <t>61,54%</t>
         </is>
       </c>
     </row>
@@ -4827,12 +4827,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>132586</t>
+          <t>133155</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>180110</t>
+          <t>176794</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4842,12 +4842,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>19,0%</t>
+          <t>19,08%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>25,81%</t>
+          <t>25,34%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4862,12 +4862,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>80062</t>
+          <t>80968</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>117433</t>
+          <t>119209</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4877,12 +4877,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>11,55%</t>
+          <t>11,69%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>16,95%</t>
+          <t>17,2%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4897,12 +4897,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>226246</t>
+          <t>222815</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>283795</t>
+          <t>282131</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4912,12 +4912,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>16,27%</t>
+          <t>16,02%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>20,41%</t>
+          <t>20,29%</t>
         </is>
       </c>
     </row>
@@ -5057,12 +5057,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>925</t>
+          <t>932</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>8263</t>
+          <t>8563</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5077,7 +5077,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>0,82%</t>
+          <t>0,85%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5092,12 +5092,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>2120</t>
+          <t>2100</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>12088</t>
+          <t>12021</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -5107,12 +5107,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0,21%</t>
+          <t>0,2%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>1,18%</t>
+          <t>1,17%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5127,12 +5127,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>4030</t>
+          <t>4085</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>16228</t>
+          <t>17023</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5147,7 +5147,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,84%</t>
         </is>
       </c>
     </row>
@@ -5170,12 +5170,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>12875</t>
+          <t>13081</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>30679</t>
+          <t>32182</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -5185,12 +5185,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>1,28%</t>
+          <t>1,3%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>3,05%</t>
+          <t>3,2%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -5205,12 +5205,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>30170</t>
+          <t>31138</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>57204</t>
+          <t>56211</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -5220,12 +5220,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>2,94%</t>
+          <t>3,03%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>5,57%</t>
+          <t>5,47%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -5240,12 +5240,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>47820</t>
+          <t>47596</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>79659</t>
+          <t>80419</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -5255,12 +5255,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>2,35%</t>
+          <t>2,34%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>3,92%</t>
+          <t>3,96%</t>
         </is>
       </c>
     </row>
@@ -5283,12 +5283,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>118342</t>
+          <t>117897</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>163249</t>
+          <t>164672</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -5298,12 +5298,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>11,77%</t>
+          <t>11,73%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>16,24%</t>
+          <t>16,38%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -5318,12 +5318,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>200465</t>
+          <t>196356</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>252000</t>
+          <t>250863</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -5333,12 +5333,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>19,5%</t>
+          <t>19,1%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>24,52%</t>
+          <t>24,41%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -5353,12 +5353,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>330581</t>
+          <t>328755</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>402013</t>
+          <t>399525</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -5368,12 +5368,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>16,26%</t>
+          <t>16,17%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>19,77%</t>
+          <t>19,65%</t>
         </is>
       </c>
     </row>
@@ -5396,12 +5396,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>607418</t>
+          <t>607426</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>672376</t>
+          <t>671600</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5411,12 +5411,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>60,41%</t>
+          <t>60,42%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>66,88%</t>
+          <t>66,8%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5431,12 +5431,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>591064</t>
+          <t>590840</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>654850</t>
+          <t>653875</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5446,12 +5446,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>57,5%</t>
+          <t>57,48%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>63,71%</t>
+          <t>63,61%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5466,12 +5466,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1217983</t>
+          <t>1213245</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>1307289</t>
+          <t>1305264</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5481,12 +5481,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>59,9%</t>
+          <t>59,67%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>64,29%</t>
+          <t>64,19%</t>
         </is>
       </c>
     </row>
@@ -5509,12 +5509,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>175805</t>
+          <t>176104</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>226227</t>
+          <t>229431</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5524,12 +5524,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>17,49%</t>
+          <t>17,52%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>22,5%</t>
+          <t>22,82%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5544,12 +5544,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>112463</t>
+          <t>112067</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>159114</t>
+          <t>157196</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5559,12 +5559,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>10,94%</t>
+          <t>10,9%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>15,48%</t>
+          <t>15,29%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5579,12 +5579,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>300825</t>
+          <t>300336</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>371488</t>
+          <t>370450</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5594,12 +5594,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>14,79%</t>
+          <t>14,77%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>18,27%</t>
+          <t>18,22%</t>
         </is>
       </c>
     </row>
@@ -5744,7 +5744,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>5978</t>
+          <t>5039</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5759,7 +5759,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,68%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5774,12 +5774,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>4042</t>
+          <t>3996</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>16107</t>
+          <t>15960</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5794,7 +5794,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>2,09%</t>
+          <t>2,07%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5809,12 +5809,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>4364</t>
+          <t>4270</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>17705</t>
+          <t>17742</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5824,7 +5824,7 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,29%</t>
+          <t>0,28%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
@@ -5852,12 +5852,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>8019</t>
+          <t>7428</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>26424</t>
+          <t>26332</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5867,12 +5867,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>1,08%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>3,55%</t>
+          <t>3,54%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5887,12 +5887,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>22758</t>
+          <t>22746</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>48755</t>
+          <t>48509</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5907,7 +5907,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>6,31%</t>
+          <t>6,28%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5922,12 +5922,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>34694</t>
+          <t>35505</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>65351</t>
+          <t>64782</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5937,12 +5937,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>2,29%</t>
+          <t>2,34%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>4,31%</t>
+          <t>4,27%</t>
         </is>
       </c>
     </row>
@@ -5965,12 +5965,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>82043</t>
+          <t>82090</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>123340</t>
+          <t>123775</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -5985,7 +5985,7 @@
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>16,56%</t>
+          <t>16,62%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -6000,12 +6000,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>140885</t>
+          <t>143131</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>188959</t>
+          <t>191030</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -6015,12 +6015,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>18,24%</t>
+          <t>18,54%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>24,47%</t>
+          <t>24,74%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -6035,12 +6035,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>235501</t>
+          <t>236572</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>295558</t>
+          <t>299250</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -6050,12 +6050,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>15,52%</t>
+          <t>15,6%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>19,48%</t>
+          <t>19,73%</t>
         </is>
       </c>
     </row>
@@ -6078,12 +6078,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>398746</t>
+          <t>400062</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>454329</t>
+          <t>456859</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -6093,12 +6093,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>53,54%</t>
+          <t>53,72%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>61,0%</t>
+          <t>61,34%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -6113,12 +6113,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>402959</t>
+          <t>405213</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>461408</t>
+          <t>461360</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -6128,7 +6128,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>52,18%</t>
+          <t>52,48%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -6148,12 +6148,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>819047</t>
+          <t>819667</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>902344</t>
+          <t>896891</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -6163,12 +6163,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>53,99%</t>
+          <t>54,03%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>59,48%</t>
+          <t>59,12%</t>
         </is>
       </c>
     </row>
@@ -6191,12 +6191,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>176725</t>
+          <t>177043</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>227006</t>
+          <t>228613</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -6206,12 +6206,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>23,73%</t>
+          <t>23,77%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>30,48%</t>
+          <t>30,7%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -6226,12 +6226,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>112156</t>
+          <t>111635</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>155273</t>
+          <t>154769</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -6241,12 +6241,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>14,52%</t>
+          <t>14,46%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>20,11%</t>
+          <t>20,04%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -6261,12 +6261,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>301189</t>
+          <t>300422</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>369251</t>
+          <t>367997</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -6276,12 +6276,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>19,85%</t>
+          <t>19,8%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>24,34%</t>
+          <t>24,26%</t>
         </is>
       </c>
     </row>
@@ -6421,12 +6421,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>941</t>
+          <t>933</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>9510</t>
+          <t>9163</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -6441,7 +6441,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>1,02%</t>
+          <t>0,98%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -6456,12 +6456,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>4809</t>
+          <t>4815</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>18811</t>
+          <t>19037</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -6476,7 +6476,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>1,8%</t>
+          <t>1,83%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -6491,12 +6491,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>7637</t>
+          <t>6910</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>24657</t>
+          <t>23494</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -6506,12 +6506,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>0,39%</t>
+          <t>0,35%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>1,25%</t>
+          <t>1,19%</t>
         </is>
       </c>
     </row>
@@ -6534,12 +6534,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>15575</t>
+          <t>16017</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>38932</t>
+          <t>37695</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -6549,12 +6549,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>1,67%</t>
+          <t>1,71%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>4,17%</t>
+          <t>4,03%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -6569,12 +6569,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>35350</t>
+          <t>36113</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>64106</t>
+          <t>64619</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -6584,12 +6584,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>3,39%</t>
+          <t>3,47%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>6,15%</t>
+          <t>6,2%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -6604,12 +6604,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>56974</t>
+          <t>57220</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>93040</t>
+          <t>93921</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -6619,12 +6619,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>2,88%</t>
+          <t>2,89%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>4,71%</t>
+          <t>4,75%</t>
         </is>
       </c>
     </row>
@@ -6647,12 +6647,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>110506</t>
+          <t>113830</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>158385</t>
+          <t>154987</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -6662,12 +6662,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>11,83%</t>
+          <t>12,18%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>16,95%</t>
+          <t>16,59%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -6682,12 +6682,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>197931</t>
+          <t>199316</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>253938</t>
+          <t>255399</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -6697,12 +6697,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>18,99%</t>
+          <t>19,13%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>24,37%</t>
+          <t>24,51%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -6717,12 +6717,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>324491</t>
+          <t>321942</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>389356</t>
+          <t>390389</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -6732,12 +6732,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>16,42%</t>
+          <t>16,29%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>19,7%</t>
+          <t>19,75%</t>
         </is>
       </c>
     </row>
@@ -6760,12 +6760,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>576973</t>
+          <t>579275</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>635674</t>
+          <t>637720</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6775,12 +6775,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>61,75%</t>
+          <t>61,99%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>68,03%</t>
+          <t>68,25%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6795,12 +6795,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>633800</t>
+          <t>635313</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>697202</t>
+          <t>697586</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6810,12 +6810,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>60,82%</t>
+          <t>60,96%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>66,9%</t>
+          <t>66,94%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6830,12 +6830,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>1230165</t>
+          <t>1226218</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>1312814</t>
+          <t>1312803</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6845,7 +6845,7 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>62,24%</t>
+          <t>62,04%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
@@ -6873,12 +6873,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>144185</t>
+          <t>142839</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>190172</t>
+          <t>189154</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6888,12 +6888,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>15,43%</t>
+          <t>15,29%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>20,35%</t>
+          <t>20,24%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6908,12 +6908,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>74820</t>
+          <t>74140</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>111370</t>
+          <t>112147</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6923,12 +6923,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>7,18%</t>
+          <t>7,11%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>10,69%</t>
+          <t>10,76%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6943,12 +6943,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>230385</t>
+          <t>230681</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>290322</t>
+          <t>289380</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6958,12 +6958,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>11,66%</t>
+          <t>11,67%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>14,69%</t>
+          <t>14,64%</t>
         </is>
       </c>
     </row>
@@ -7103,12 +7103,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>4170</t>
+          <t>4469</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>17001</t>
+          <t>17684</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -7118,12 +7118,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>0,12%</t>
+          <t>0,13%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,52%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -7138,12 +7138,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>19178</t>
+          <t>19862</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>40871</t>
+          <t>41795</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -7153,12 +7153,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>0,54%</t>
+          <t>0,56%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>1,16%</t>
+          <t>1,18%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -7173,12 +7173,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>27653</t>
+          <t>26642</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>52224</t>
+          <t>51861</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -7188,7 +7188,7 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,39%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
@@ -7216,12 +7216,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>60568</t>
+          <t>62231</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>98971</t>
+          <t>100909</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -7231,12 +7231,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>1,79%</t>
+          <t>1,84%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>2,93%</t>
+          <t>2,98%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -7251,12 +7251,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>138398</t>
+          <t>138437</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>190279</t>
+          <t>189723</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -7266,12 +7266,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>3,91%</t>
+          <t>3,92%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>5,38%</t>
+          <t>5,37%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -7286,12 +7286,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>212927</t>
+          <t>209932</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>275397</t>
+          <t>274056</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -7301,12 +7301,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>3,08%</t>
+          <t>3,03%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>3,98%</t>
+          <t>3,96%</t>
         </is>
       </c>
     </row>
@@ -7329,12 +7329,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>442746</t>
+          <t>442474</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>525838</t>
+          <t>529869</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -7344,12 +7344,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>13,09%</t>
+          <t>13,08%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>15,55%</t>
+          <t>15,67%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -7364,12 +7364,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>714030</t>
+          <t>713135</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>814126</t>
+          <t>811339</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -7379,12 +7379,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>20,2%</t>
+          <t>20,17%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>23,03%</t>
+          <t>22,95%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -7399,12 +7399,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>1180483</t>
+          <t>1176775</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>1315836</t>
+          <t>1310390</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -7414,12 +7414,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>17,07%</t>
+          <t>17,01%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>19,02%</t>
+          <t>18,94%</t>
         </is>
       </c>
     </row>
@@ -7442,12 +7442,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>2030004</t>
+          <t>2028477</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>2150144</t>
+          <t>2147727</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -7457,12 +7457,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>60,02%</t>
+          <t>59,97%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>63,57%</t>
+          <t>63,5%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -7477,12 +7477,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>2065792</t>
+          <t>2062875</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>2186627</t>
+          <t>2185424</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -7492,12 +7492,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>58,44%</t>
+          <t>58,35%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>61,85%</t>
+          <t>61,82%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -7512,12 +7512,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>4128904</t>
+          <t>4134438</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>4297481</t>
+          <t>4296547</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -7527,12 +7527,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>59,69%</t>
+          <t>59,77%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>62,12%</t>
+          <t>62,11%</t>
         </is>
       </c>
     </row>
@@ -7555,12 +7555,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>669865</t>
+          <t>674234</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>768810</t>
+          <t>771165</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -7570,12 +7570,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>19,8%</t>
+          <t>19,93%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>22,73%</t>
+          <t>22,8%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -7590,12 +7590,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>418145</t>
+          <t>416333</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>508402</t>
+          <t>497352</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -7605,12 +7605,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>11,83%</t>
+          <t>11,78%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>14,38%</t>
+          <t>14,07%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -7625,12 +7625,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>1118531</t>
+          <t>1121460</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>1249193</t>
+          <t>1246274</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -7640,12 +7640,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>16,17%</t>
+          <t>16,21%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>18,06%</t>
+          <t>18,02%</t>
         </is>
       </c>
     </row>
@@ -7822,7 +7822,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según su salud autopercibida en los últimos 12 meses en 2016</t>
+          <t>Población según su salud autopercibida en los últimos 12 meses en 2016 (tasa de respuesta: 99,22%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -8017,12 +8017,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>1683</t>
+          <t>1721</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>9770</t>
+          <t>10235</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -8032,12 +8032,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,25%</t>
+          <t>0,26%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>1,46%</t>
+          <t>1,53%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -8057,7 +8057,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>6822</t>
+          <t>7997</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -8072,7 +8072,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>1,02%</t>
+          <t>1,2%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -8087,12 +8087,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>2866</t>
+          <t>2650</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>13329</t>
+          <t>12598</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -8102,12 +8102,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,21%</t>
+          <t>0,2%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>0,94%</t>
         </is>
       </c>
     </row>
@@ -8130,12 +8130,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>9391</t>
+          <t>9288</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>25860</t>
+          <t>25409</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -8145,12 +8145,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>1,4%</t>
+          <t>1,39%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>3,86%</t>
+          <t>3,79%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -8165,12 +8165,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>31693</t>
+          <t>31176</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>57564</t>
+          <t>57120</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -8180,12 +8180,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>4,74%</t>
+          <t>4,66%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>8,61%</t>
+          <t>8,54%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -8200,12 +8200,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>44583</t>
+          <t>45405</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>74990</t>
+          <t>75949</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -8215,12 +8215,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>3,33%</t>
+          <t>3,39%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>5,6%</t>
+          <t>5,68%</t>
         </is>
       </c>
     </row>
@@ -8243,12 +8243,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>78783</t>
+          <t>78220</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>113761</t>
+          <t>113469</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -8258,12 +8258,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>11,77%</t>
+          <t>11,68%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>16,99%</t>
+          <t>16,95%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -8278,12 +8278,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>127803</t>
+          <t>129150</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>172897</t>
+          <t>171717</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -8293,12 +8293,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>19,12%</t>
+          <t>19,32%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>25,86%</t>
+          <t>25,68%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -8313,12 +8313,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>217920</t>
+          <t>216972</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>276277</t>
+          <t>273680</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -8328,12 +8328,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>16,28%</t>
+          <t>16,21%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>20,65%</t>
+          <t>20,45%</t>
         </is>
       </c>
     </row>
@@ -8356,12 +8356,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>356663</t>
+          <t>354138</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>407174</t>
+          <t>405601</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -8371,12 +8371,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>53,27%</t>
+          <t>52,89%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>60,81%</t>
+          <t>60,57%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -8391,12 +8391,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>312280</t>
+          <t>311382</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>365519</t>
+          <t>363106</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -8406,12 +8406,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>46,71%</t>
+          <t>46,57%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>54,67%</t>
+          <t>54,31%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -8426,12 +8426,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>680758</t>
+          <t>683275</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>755936</t>
+          <t>753358</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -8441,12 +8441,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>50,87%</t>
+          <t>51,06%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>56,49%</t>
+          <t>56,3%</t>
         </is>
       </c>
     </row>
@@ -8469,12 +8469,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>152426</t>
+          <t>153605</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>196908</t>
+          <t>199107</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -8484,12 +8484,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>22,76%</t>
+          <t>22,94%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>29,41%</t>
+          <t>29,74%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -8504,12 +8504,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>116496</t>
+          <t>117473</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>158283</t>
+          <t>158846</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -8519,12 +8519,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>17,42%</t>
+          <t>17,57%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>23,67%</t>
+          <t>23,76%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -8539,12 +8539,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>277690</t>
+          <t>278741</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>339494</t>
+          <t>340062</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -8554,12 +8554,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>20,75%</t>
+          <t>20,83%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>25,37%</t>
+          <t>25,41%</t>
         </is>
       </c>
     </row>
@@ -8704,7 +8704,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>4584</t>
+          <t>4565</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -8734,12 +8734,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>927</t>
+          <t>930</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>8891</t>
+          <t>9467</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -8754,7 +8754,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>0,86%</t>
+          <t>0,92%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -8769,12 +8769,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>1023</t>
+          <t>1020</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>10431</t>
+          <t>10237</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -8789,7 +8789,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>0,51%</t>
+          <t>0,5%</t>
         </is>
       </c>
     </row>
@@ -8812,12 +8812,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>13570</t>
+          <t>13906</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>32604</t>
+          <t>31564</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -8827,12 +8827,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>1,33%</t>
+          <t>1,37%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>3,2%</t>
+          <t>3,1%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -8847,12 +8847,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>23146</t>
+          <t>22582</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>49071</t>
+          <t>48706</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -8862,12 +8862,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>2,24%</t>
+          <t>2,18%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>4,75%</t>
+          <t>4,71%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -8882,12 +8882,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>40902</t>
+          <t>40317</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>72625</t>
+          <t>72401</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -8897,12 +8897,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>1,99%</t>
+          <t>1,96%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>3,54%</t>
+          <t>3,53%</t>
         </is>
       </c>
     </row>
@@ -8925,12 +8925,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>115466</t>
+          <t>115892</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>158407</t>
+          <t>160288</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -8940,12 +8940,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>11,34%</t>
+          <t>11,38%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>15,55%</t>
+          <t>15,74%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -8960,12 +8960,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>190369</t>
+          <t>189227</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>247633</t>
+          <t>247278</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -8975,12 +8975,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>18,41%</t>
+          <t>18,3%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>23,95%</t>
+          <t>23,91%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -8995,12 +8995,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>321420</t>
+          <t>318909</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>391832</t>
+          <t>388529</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -9010,12 +9010,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>15,66%</t>
+          <t>15,54%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>19,09%</t>
+          <t>18,93%</t>
         </is>
       </c>
     </row>
@@ -9038,12 +9038,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>571032</t>
+          <t>568911</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>635046</t>
+          <t>635395</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -9053,12 +9053,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>56,07%</t>
+          <t>55,86%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>62,35%</t>
+          <t>62,38%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -9073,12 +9073,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>570335</t>
+          <t>570473</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>635193</t>
+          <t>639135</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -9088,12 +9088,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>55,15%</t>
+          <t>55,17%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>61,43%</t>
+          <t>61,81%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -9108,12 +9108,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1160265</t>
+          <t>1156019</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>1258377</t>
+          <t>1255095</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -9123,12 +9123,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>56,53%</t>
+          <t>56,32%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>61,31%</t>
+          <t>61,15%</t>
         </is>
       </c>
     </row>
@@ -9151,12 +9151,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>230349</t>
+          <t>229353</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>288025</t>
+          <t>288209</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -9166,12 +9166,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>22,62%</t>
+          <t>22,52%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>28,28%</t>
+          <t>28,3%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -9186,12 +9186,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>151947</t>
+          <t>150367</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>201799</t>
+          <t>198704</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -9201,12 +9201,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>14,69%</t>
+          <t>14,54%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>19,51%</t>
+          <t>19,22%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -9221,12 +9221,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>393624</t>
+          <t>395174</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>470113</t>
+          <t>472989</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -9236,12 +9236,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>19,18%</t>
+          <t>19,25%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>22,9%</t>
+          <t>23,04%</t>
         </is>
       </c>
     </row>
@@ -9386,7 +9386,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>11004</t>
+          <t>11121</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -9401,7 +9401,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>1,45%</t>
+          <t>1,47%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -9416,12 +9416,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>3333</t>
+          <t>3526</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>16016</t>
+          <t>16660</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -9431,12 +9431,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0,43%</t>
+          <t>0,45%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>2,06%</t>
+          <t>2,14%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -9451,12 +9451,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>5682</t>
+          <t>5280</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>22546</t>
+          <t>21172</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -9466,12 +9466,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,37%</t>
+          <t>0,34%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>1,47%</t>
+          <t>1,38%</t>
         </is>
       </c>
     </row>
@@ -9494,12 +9494,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>9321</t>
+          <t>9642</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>25008</t>
+          <t>25540</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -9509,12 +9509,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>1,23%</t>
+          <t>1,27%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>3,3%</t>
+          <t>3,37%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -9529,12 +9529,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>22652</t>
+          <t>23071</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>46091</t>
+          <t>46276</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -9544,12 +9544,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>2,91%</t>
+          <t>2,97%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>5,93%</t>
+          <t>5,95%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -9564,12 +9564,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>36027</t>
+          <t>35986</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>63824</t>
+          <t>67717</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -9579,12 +9579,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>2,35%</t>
+          <t>2,34%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>4,16%</t>
+          <t>4,41%</t>
         </is>
       </c>
     </row>
@@ -9607,12 +9607,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>80989</t>
+          <t>80786</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>118875</t>
+          <t>118230</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -9622,12 +9622,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>10,68%</t>
+          <t>10,65%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>15,67%</t>
+          <t>15,59%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -9642,12 +9642,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>110024</t>
+          <t>109216</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>152013</t>
+          <t>154388</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -9657,12 +9657,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>14,16%</t>
+          <t>14,05%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>19,56%</t>
+          <t>19,87%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -9677,12 +9677,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>203255</t>
+          <t>200784</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>263719</t>
+          <t>256399</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -9692,12 +9692,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>13,24%</t>
+          <t>13,08%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>17,17%</t>
+          <t>16,7%</t>
         </is>
       </c>
     </row>
@@ -9720,12 +9720,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>422022</t>
+          <t>421813</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>476824</t>
+          <t>477016</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -9735,12 +9735,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>55,64%</t>
+          <t>55,62%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>62,87%</t>
+          <t>62,9%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -9755,12 +9755,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>411125</t>
+          <t>412691</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>467746</t>
+          <t>469231</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -9770,12 +9770,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>52,9%</t>
+          <t>53,1%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>60,19%</t>
+          <t>60,38%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -9790,12 +9790,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>851475</t>
+          <t>843901</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>931543</t>
+          <t>925611</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -9805,12 +9805,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>55,45%</t>
+          <t>54,96%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>60,66%</t>
+          <t>60,28%</t>
         </is>
       </c>
     </row>
@@ -9833,12 +9833,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>167952</t>
+          <t>165419</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>215591</t>
+          <t>217150</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -9848,12 +9848,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>22,14%</t>
+          <t>21,81%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>28,43%</t>
+          <t>28,63%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -9868,12 +9868,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>142349</t>
+          <t>141910</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>187607</t>
+          <t>187185</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -9883,12 +9883,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>18,32%</t>
+          <t>18,26%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>24,14%</t>
+          <t>24,09%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -9903,12 +9903,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>325106</t>
+          <t>321495</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>390091</t>
+          <t>391117</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -9918,12 +9918,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>21,17%</t>
+          <t>20,94%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>25,4%</t>
+          <t>25,47%</t>
         </is>
       </c>
     </row>
@@ -10068,7 +10068,7 @@
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>6620</t>
+          <t>6356</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -10083,7 +10083,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>0,71%</t>
+          <t>0,69%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -10098,12 +10098,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>3424</t>
+          <t>3389</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>16278</t>
+          <t>16160</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -10118,7 +10118,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>1,57%</t>
+          <t>1,56%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -10133,12 +10133,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>4873</t>
+          <t>5360</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>18072</t>
+          <t>18587</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -10148,12 +10148,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>0,25%</t>
+          <t>0,27%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>0,92%</t>
+          <t>0,95%</t>
         </is>
       </c>
     </row>
@@ -10176,12 +10176,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>12467</t>
+          <t>12384</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>31655</t>
+          <t>32303</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -10191,12 +10191,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>1,35%</t>
+          <t>1,34%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>3,42%</t>
+          <t>3,49%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -10211,12 +10211,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>29324</t>
+          <t>30023</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>56218</t>
+          <t>56355</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -10226,12 +10226,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>2,83%</t>
+          <t>2,9%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>5,43%</t>
+          <t>5,45%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -10246,12 +10246,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>47403</t>
+          <t>46189</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>81438</t>
+          <t>80633</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -10261,12 +10261,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>2,42%</t>
+          <t>2,36%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>4,15%</t>
+          <t>4,11%</t>
         </is>
       </c>
     </row>
@@ -10289,12 +10289,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>105375</t>
+          <t>106004</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>146762</t>
+          <t>144162</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -10304,12 +10304,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>11,37%</t>
+          <t>11,44%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>15,84%</t>
+          <t>15,56%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -10324,12 +10324,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>185660</t>
+          <t>184906</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>242109</t>
+          <t>242581</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -10339,12 +10339,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>17,95%</t>
+          <t>17,87%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>23,4%</t>
+          <t>23,45%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -10359,12 +10359,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>303782</t>
+          <t>301805</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>373935</t>
+          <t>371872</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -10374,12 +10374,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>15,49%</t>
+          <t>15,39%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>19,07%</t>
+          <t>18,96%</t>
         </is>
       </c>
     </row>
@@ -10402,12 +10402,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>518063</t>
+          <t>516389</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>576551</t>
+          <t>575801</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -10417,12 +10417,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>55,91%</t>
+          <t>55,72%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>62,22%</t>
+          <t>62,14%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -10437,12 +10437,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>561820</t>
+          <t>560239</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>627006</t>
+          <t>626508</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -10452,12 +10452,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>54,31%</t>
+          <t>54,16%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>60,61%</t>
+          <t>60,56%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -10472,12 +10472,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>1095462</t>
+          <t>1087421</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>1187342</t>
+          <t>1179147</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -10487,12 +10487,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>55,86%</t>
+          <t>55,45%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>60,54%</t>
+          <t>60,12%</t>
         </is>
       </c>
     </row>
@@ -10515,12 +10515,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>208178</t>
+          <t>205316</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>261331</t>
+          <t>258593</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -10530,12 +10530,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>22,46%</t>
+          <t>22,16%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>28,2%</t>
+          <t>27,91%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -10550,12 +10550,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>156592</t>
+          <t>156790</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>205412</t>
+          <t>203173</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -10565,12 +10565,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>15,14%</t>
+          <t>15,16%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>19,86%</t>
+          <t>19,64%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -10585,12 +10585,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>374750</t>
+          <t>376201</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>446633</t>
+          <t>448988</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -10600,12 +10600,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>19,11%</t>
+          <t>19,18%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>22,77%</t>
+          <t>22,89%</t>
         </is>
       </c>
     </row>
@@ -10745,12 +10745,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>5168</t>
+          <t>5192</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>18621</t>
+          <t>19122</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -10765,7 +10765,7 @@
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>0,55%</t>
+          <t>0,57%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -10780,12 +10780,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>13566</t>
+          <t>12831</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>33343</t>
+          <t>32428</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -10795,12 +10795,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>0,39%</t>
+          <t>0,37%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>0,95%</t>
+          <t>0,92%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -10815,12 +10815,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>21347</t>
+          <t>21192</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>44307</t>
+          <t>44785</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -10835,7 +10835,7 @@
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>0,64%</t>
+          <t>0,65%</t>
         </is>
       </c>
     </row>
@@ -10858,12 +10858,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>57409</t>
+          <t>57787</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>93492</t>
+          <t>93125</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -10873,12 +10873,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>1,7%</t>
+          <t>1,71%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>2,77%</t>
+          <t>2,76%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -10893,12 +10893,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>128414</t>
+          <t>128500</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>179431</t>
+          <t>180626</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -10908,12 +10908,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>3,65%</t>
+          <t>3,66%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>5,11%</t>
+          <t>5,14%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -10928,12 +10928,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>197491</t>
+          <t>196374</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>256372</t>
+          <t>259414</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -10943,12 +10943,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>2,87%</t>
+          <t>2,85%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>3,72%</t>
+          <t>3,77%</t>
         </is>
       </c>
     </row>
@@ -10971,12 +10971,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>416421</t>
+          <t>416746</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>499977</t>
+          <t>497109</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -10986,12 +10986,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>12,34%</t>
+          <t>12,35%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>14,82%</t>
+          <t>14,74%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -11006,12 +11006,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>662046</t>
+          <t>660771</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>763112</t>
+          <t>766540</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -11021,12 +11021,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>18,84%</t>
+          <t>18,8%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>21,71%</t>
+          <t>21,81%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -11041,12 +11041,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>1104158</t>
+          <t>1102679</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>1232268</t>
+          <t>1230578</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -11056,12 +11056,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>16,03%</t>
+          <t>16,01%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>17,89%</t>
+          <t>17,87%</t>
         </is>
       </c>
     </row>
@@ -11084,12 +11084,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>1923001</t>
+          <t>1922226</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>2037629</t>
+          <t>2037363</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -11099,12 +11099,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>57,01%</t>
+          <t>56,99%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>60,41%</t>
+          <t>60,4%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -11119,12 +11119,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>1917912</t>
+          <t>1912047</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>2034881</t>
+          <t>2039684</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -11134,12 +11134,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>54,57%</t>
+          <t>54,41%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>57,9%</t>
+          <t>58,04%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -11154,12 +11154,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>3880094</t>
+          <t>3874916</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>4032719</t>
+          <t>4034836</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -11169,12 +11169,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>56,34%</t>
+          <t>56,26%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>58,55%</t>
+          <t>58,58%</t>
         </is>
       </c>
     </row>
@@ -11197,12 +11197,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>802562</t>
+          <t>806633</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>907920</t>
+          <t>903410</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -11212,12 +11212,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>23,79%</t>
+          <t>23,91%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>26,92%</t>
+          <t>26,78%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -11232,12 +11232,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>612937</t>
+          <t>604596</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>703586</t>
+          <t>699330</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -11247,12 +11247,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>17,44%</t>
+          <t>17,2%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>20,02%</t>
+          <t>19,9%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -11267,12 +11267,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>1445729</t>
+          <t>1444663</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>1584094</t>
+          <t>1579264</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -11282,12 +11282,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>20,99%</t>
+          <t>20,98%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>23,0%</t>
+          <t>22,93%</t>
         </is>
       </c>
     </row>
@@ -11464,7 +11464,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según su salud autopercibida en los últimos 12 meses en 2023</t>
+          <t>Población según su salud autopercibida en los últimos 12 meses en 2023 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -11659,12 +11659,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>3429</t>
+          <t>3285</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>13625</t>
+          <t>13791</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -11674,12 +11674,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,54%</t>
+          <t>0,52%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>2,14%</t>
+          <t>2,17%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -11694,12 +11694,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>6822</t>
+          <t>6850</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>15617</t>
+          <t>15775</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -11714,7 +11714,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>2,31%</t>
+          <t>2,34%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -11729,12 +11729,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>11939</t>
+          <t>12219</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>25635</t>
+          <t>25521</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -11744,12 +11744,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,91%</t>
+          <t>0,93%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>1,96%</t>
+          <t>1,95%</t>
         </is>
       </c>
     </row>
@@ -11772,12 +11772,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>21764</t>
+          <t>22188</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>39802</t>
+          <t>39291</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -11787,12 +11787,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>3,43%</t>
+          <t>3,49%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>6,26%</t>
+          <t>6,18%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -11807,12 +11807,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>38451</t>
+          <t>39073</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>56346</t>
+          <t>57590</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -11822,12 +11822,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>5,69%</t>
+          <t>5,79%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>8,34%</t>
+          <t>8,53%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -11842,12 +11842,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>65568</t>
+          <t>65814</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>91574</t>
+          <t>90397</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -11857,12 +11857,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>5,0%</t>
+          <t>5,02%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>6,99%</t>
+          <t>6,9%</t>
         </is>
       </c>
     </row>
@@ -11885,12 +11885,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>95992</t>
+          <t>95618</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>131565</t>
+          <t>132862</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -11900,12 +11900,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>15,11%</t>
+          <t>15,05%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>20,7%</t>
+          <t>20,91%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -11920,12 +11920,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>136940</t>
+          <t>135637</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>170067</t>
+          <t>168037</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -11935,12 +11935,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>20,28%</t>
+          <t>20,08%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>25,18%</t>
+          <t>24,88%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -11955,12 +11955,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>240349</t>
+          <t>239525</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>288602</t>
+          <t>288632</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -11970,7 +11970,7 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>18,34%</t>
+          <t>18,27%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
@@ -11998,12 +11998,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>367243</t>
+          <t>368129</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>422604</t>
+          <t>422445</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -12013,12 +12013,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>57,79%</t>
+          <t>57,93%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>66,51%</t>
+          <t>66,48%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -12033,12 +12033,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>382368</t>
+          <t>383421</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>420915</t>
+          <t>421827</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -12048,12 +12048,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>56,62%</t>
+          <t>56,77%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>62,32%</t>
+          <t>62,46%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -12068,12 +12068,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>765569</t>
+          <t>762953</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>831396</t>
+          <t>834426</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -12083,12 +12083,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>58,4%</t>
+          <t>58,2%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>63,43%</t>
+          <t>63,66%</t>
         </is>
       </c>
     </row>
@@ -12111,12 +12111,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>67774</t>
+          <t>67501</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>118490</t>
+          <t>121849</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -12126,12 +12126,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>10,67%</t>
+          <t>10,62%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>18,65%</t>
+          <t>19,18%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -12146,12 +12146,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>50728</t>
+          <t>50690</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>78470</t>
+          <t>77019</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -12166,7 +12166,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>11,62%</t>
+          <t>11,4%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -12181,12 +12181,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>127160</t>
+          <t>126840</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>186609</t>
+          <t>187036</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -12196,12 +12196,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>9,7%</t>
+          <t>9,68%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>14,24%</t>
+          <t>14,27%</t>
         </is>
       </c>
     </row>
@@ -12341,12 +12341,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>3984</t>
+          <t>4788</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>18003</t>
+          <t>18195</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -12356,12 +12356,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,33%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>1,51%</t>
+          <t>1,53%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -12376,12 +12376,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>9541</t>
+          <t>9588</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>20701</t>
+          <t>19956</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -12396,7 +12396,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>2,16%</t>
+          <t>2,08%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -12411,12 +12411,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>15796</t>
+          <t>14873</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>33219</t>
+          <t>33388</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -12426,12 +12426,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,73%</t>
+          <t>0,69%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>1,54%</t>
+          <t>1,55%</t>
         </is>
       </c>
     </row>
@@ -12454,12 +12454,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>15481</t>
+          <t>14921</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>44259</t>
+          <t>44327</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -12469,12 +12469,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>1,25%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>3,71%</t>
+          <t>3,72%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -12489,12 +12489,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>42212</t>
+          <t>40971</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>60988</t>
+          <t>61258</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -12504,12 +12504,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>4,41%</t>
+          <t>4,28%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>6,37%</t>
+          <t>6,39%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -12524,12 +12524,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>51980</t>
+          <t>54579</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>98605</t>
+          <t>98463</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -12539,7 +12539,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>2,42%</t>
+          <t>2,54%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -12567,12 +12567,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>66362</t>
+          <t>53417</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>157767</t>
+          <t>156550</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -12582,12 +12582,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>5,56%</t>
+          <t>4,48%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>13,23%</t>
+          <t>13,12%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -12602,12 +12602,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>181841</t>
+          <t>180999</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>222533</t>
+          <t>220399</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -12617,12 +12617,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>18,98%</t>
+          <t>18,89%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>23,23%</t>
+          <t>23,0%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -12637,12 +12637,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>211065</t>
+          <t>210473</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>370274</t>
+          <t>370418</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -12652,12 +12652,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>9,81%</t>
+          <t>9,79%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>17,21%</t>
+          <t>17,22%</t>
         </is>
       </c>
     </row>
@@ -12680,12 +12680,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>729887</t>
+          <t>727826</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>990692</t>
+          <t>1028461</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -12695,12 +12695,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>61,19%</t>
+          <t>61,02%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>83,05%</t>
+          <t>86,22%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -12715,12 +12715,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>558128</t>
+          <t>555704</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>610631</t>
+          <t>607575</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -12730,12 +12730,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>58,25%</t>
+          <t>58,0%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>63,73%</t>
+          <t>63,41%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -12750,12 +12750,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1310604</t>
+          <t>1307223</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>1661035</t>
+          <t>1665716</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -12765,12 +12765,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>60,93%</t>
+          <t>60,77%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>77,22%</t>
+          <t>77,44%</t>
         </is>
       </c>
     </row>
@@ -12793,12 +12793,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>107531</t>
+          <t>94075</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>266447</t>
+          <t>270882</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -12808,12 +12808,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>9,01%</t>
+          <t>7,89%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>22,34%</t>
+          <t>22,71%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -12828,12 +12828,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>91238</t>
+          <t>92243</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>130755</t>
+          <t>130711</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -12843,12 +12843,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>9,52%</t>
+          <t>9,63%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>13,65%</t>
+          <t>13,64%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -12863,12 +12863,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>206443</t>
+          <t>202744</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>367076</t>
+          <t>372976</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -12878,12 +12878,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>9,6%</t>
+          <t>9,43%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>17,07%</t>
+          <t>17,34%</t>
         </is>
       </c>
     </row>
@@ -13023,12 +13023,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>4249</t>
+          <t>4003</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>17244</t>
+          <t>16883</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -13038,12 +13038,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,57%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>2,45%</t>
+          <t>2,4%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -13058,12 +13058,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>2174</t>
+          <t>2076</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>12500</t>
+          <t>12492</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -13073,7 +13073,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0,23%</t>
+          <t>0,22%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -13093,12 +13093,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>8427</t>
+          <t>8396</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>25079</t>
+          <t>25282</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -13113,7 +13113,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>1,53%</t>
+          <t>1,54%</t>
         </is>
       </c>
     </row>
@@ -13136,12 +13136,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>10858</t>
+          <t>9830</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>25323</t>
+          <t>25676</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -13151,12 +13151,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>1,54%</t>
+          <t>1,39%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>3,59%</t>
+          <t>3,64%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -13171,12 +13171,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>14476</t>
+          <t>13437</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>43280</t>
+          <t>42896</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -13186,12 +13186,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>1,55%</t>
+          <t>1,44%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>4,64%</t>
+          <t>4,6%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -13206,12 +13206,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>29699</t>
+          <t>30529</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>60237</t>
+          <t>61203</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -13221,12 +13221,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>1,81%</t>
+          <t>1,86%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>3,68%</t>
+          <t>3,74%</t>
         </is>
       </c>
     </row>
@@ -13249,12 +13249,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>85972</t>
+          <t>86465</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>125952</t>
+          <t>126405</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -13264,12 +13264,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>12,2%</t>
+          <t>12,27%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>17,87%</t>
+          <t>17,94%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -13284,12 +13284,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>73907</t>
+          <t>63837</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>185215</t>
+          <t>184782</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -13299,12 +13299,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>7,92%</t>
+          <t>6,84%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>19,84%</t>
+          <t>19,8%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -13319,12 +13319,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>163019</t>
+          <t>164653</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>284320</t>
+          <t>287605</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -13334,12 +13334,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>9,95%</t>
+          <t>10,05%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>17,36%</t>
+          <t>17,56%</t>
         </is>
       </c>
     </row>
@@ -13362,12 +13362,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>402504</t>
+          <t>406240</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>463272</t>
+          <t>463194</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -13377,12 +13377,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>57,12%</t>
+          <t>57,65%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>65,74%</t>
+          <t>65,73%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -13397,12 +13397,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>541986</t>
+          <t>537713</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>775043</t>
+          <t>782789</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -13412,12 +13412,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>58,07%</t>
+          <t>57,61%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>83,04%</t>
+          <t>83,87%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -13432,12 +13432,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>981697</t>
+          <t>973250</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>1264061</t>
+          <t>1253876</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -13447,12 +13447,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>59,93%</t>
+          <t>59,42%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>77,17%</t>
+          <t>76,55%</t>
         </is>
       </c>
     </row>
@@ -13475,12 +13475,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>113494</t>
+          <t>114401</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>168993</t>
+          <t>168475</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -13490,12 +13490,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>16,11%</t>
+          <t>16,23%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>23,98%</t>
+          <t>23,91%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -13510,12 +13510,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>61580</t>
+          <t>62369</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>204405</t>
+          <t>223226</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -13525,12 +13525,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>6,6%</t>
+          <t>6,68%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>21,9%</t>
+          <t>23,92%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -13545,12 +13545,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>169871</t>
+          <t>179155</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>338151</t>
+          <t>354812</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -13560,12 +13560,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>10,37%</t>
+          <t>10,94%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>20,64%</t>
+          <t>21,66%</t>
         </is>
       </c>
     </row>
@@ -13705,12 +13705,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>5220</t>
+          <t>4983</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>18488</t>
+          <t>18200</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -13720,12 +13720,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>0,56%</t>
+          <t>0,54%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>1,99%</t>
+          <t>1,96%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -13740,12 +13740,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>7812</t>
+          <t>8632</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>20302</t>
+          <t>20448</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -13755,12 +13755,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>0,71%</t>
+          <t>0,79%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>1,85%</t>
+          <t>1,87%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -13775,12 +13775,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>16724</t>
+          <t>16188</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>33503</t>
+          <t>34412</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -13790,12 +13790,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>0,83%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>1,66%</t>
+          <t>1,7%</t>
         </is>
       </c>
     </row>
@@ -13818,12 +13818,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>22419</t>
+          <t>22807</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>43893</t>
+          <t>43542</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -13833,12 +13833,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>2,42%</t>
+          <t>2,46%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>4,74%</t>
+          <t>4,7%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -13853,12 +13853,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>41409</t>
+          <t>42837</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>66519</t>
+          <t>68479</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -13868,12 +13868,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>3,78%</t>
+          <t>3,91%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>6,08%</t>
+          <t>6,25%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -13888,12 +13888,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>70942</t>
+          <t>71440</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>102295</t>
+          <t>103005</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -13903,12 +13903,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>3,51%</t>
+          <t>3,53%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>5,06%</t>
+          <t>5,09%</t>
         </is>
       </c>
     </row>
@@ -13931,12 +13931,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>118333</t>
+          <t>121890</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>161611</t>
+          <t>163288</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -13946,12 +13946,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>12,77%</t>
+          <t>13,15%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>17,44%</t>
+          <t>17,62%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -13966,12 +13966,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>224906</t>
+          <t>225575</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>439205</t>
+          <t>443199</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -13981,12 +13981,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>20,54%</t>
+          <t>20,6%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>40,11%</t>
+          <t>40,48%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -14001,12 +14001,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>361435</t>
+          <t>360583</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>639971</t>
+          <t>620360</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -14016,12 +14016,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>17,88%</t>
+          <t>17,84%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>31,65%</t>
+          <t>30,68%</t>
         </is>
       </c>
     </row>
@@ -14044,12 +14044,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>535404</t>
+          <t>532916</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>599693</t>
+          <t>599093</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -14059,12 +14059,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>57,77%</t>
+          <t>57,5%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>64,7%</t>
+          <t>64,64%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -14079,12 +14079,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>514598</t>
+          <t>510261</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>688875</t>
+          <t>687532</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -14094,12 +14094,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>47,0%</t>
+          <t>46,6%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>62,91%</t>
+          <t>62,79%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -14114,12 +14114,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>1061652</t>
+          <t>1058553</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>1263398</t>
+          <t>1266123</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -14129,12 +14129,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>52,51%</t>
+          <t>52,36%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>62,49%</t>
+          <t>62,62%</t>
         </is>
       </c>
     </row>
@@ -14157,12 +14157,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>150633</t>
+          <t>149747</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>210493</t>
+          <t>211984</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -14172,12 +14172,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>16,25%</t>
+          <t>16,16%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>22,71%</t>
+          <t>22,87%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -14192,12 +14192,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>79267</t>
+          <t>80514</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>126345</t>
+          <t>124811</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -14207,12 +14207,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>7,24%</t>
+          <t>7,35%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>11,54%</t>
+          <t>11,4%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -14227,12 +14227,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>241734</t>
+          <t>237307</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>322814</t>
+          <t>319842</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -14242,12 +14242,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>11,96%</t>
+          <t>11,74%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>15,97%</t>
+          <t>15,82%</t>
         </is>
       </c>
     </row>
@@ -14387,12 +14387,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>25372</t>
+          <t>24635</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>51631</t>
+          <t>49269</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -14402,12 +14402,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>0,73%</t>
+          <t>0,71%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>1,49%</t>
+          <t>1,42%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -14422,12 +14422,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>33181</t>
+          <t>33979</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>55873</t>
+          <t>57409</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -14437,47 +14437,47 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
+          <t>0,93%</t>
+        </is>
+      </c>
+      <c r="P28" s="2" t="inlineStr">
+        <is>
+          <t>1,57%</t>
+        </is>
+      </c>
+      <c r="Q28" s="2" t="inlineStr">
+        <is>
+          <t>131</t>
+        </is>
+      </c>
+      <c r="R28" s="2" t="inlineStr">
+        <is>
+          <t>80748</t>
+        </is>
+      </c>
+      <c r="S28" s="2" t="inlineStr">
+        <is>
+          <t>64645</t>
+        </is>
+      </c>
+      <c r="T28" s="2" t="inlineStr">
+        <is>
+          <t>97202</t>
+        </is>
+      </c>
+      <c r="U28" s="2" t="inlineStr">
+        <is>
+          <t>1,13%</t>
+        </is>
+      </c>
+      <c r="V28" s="2" t="inlineStr">
+        <is>
           <t>0,91%</t>
         </is>
       </c>
-      <c r="P28" s="2" t="inlineStr">
-        <is>
-          <t>1,53%</t>
-        </is>
-      </c>
-      <c r="Q28" s="2" t="inlineStr">
-        <is>
-          <t>131</t>
-        </is>
-      </c>
-      <c r="R28" s="2" t="inlineStr">
-        <is>
-          <t>80748</t>
-        </is>
-      </c>
-      <c r="S28" s="2" t="inlineStr">
-        <is>
-          <t>65271</t>
-        </is>
-      </c>
-      <c r="T28" s="2" t="inlineStr">
-        <is>
-          <t>99752</t>
-        </is>
-      </c>
-      <c r="U28" s="2" t="inlineStr">
-        <is>
-          <t>1,13%</t>
-        </is>
-      </c>
-      <c r="V28" s="2" t="inlineStr">
-        <is>
-          <t>0,92%</t>
-        </is>
-      </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>1,4%</t>
+          <t>1,36%</t>
         </is>
       </c>
     </row>
@@ -14500,12 +14500,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>82787</t>
+          <t>80180</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>128827</t>
+          <t>127855</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -14515,12 +14515,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>2,39%</t>
+          <t>2,32%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>3,72%</t>
+          <t>3,7%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -14535,12 +14535,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>143377</t>
+          <t>148327</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>206197</t>
+          <t>206672</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -14550,12 +14550,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>3,92%</t>
+          <t>4,05%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>5,63%</t>
+          <t>5,64%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -14570,12 +14570,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>250906</t>
+          <t>248298</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>323322</t>
+          <t>324741</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -14585,12 +14585,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>3,52%</t>
+          <t>3,49%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>4,54%</t>
+          <t>4,56%</t>
         </is>
       </c>
     </row>
@@ -14613,12 +14613,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>374825</t>
+          <t>374703</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>533833</t>
+          <t>530141</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -14633,7 +14633,7 @@
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>15,43%</t>
+          <t>15,32%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -14648,12 +14648,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>660553</t>
+          <t>661365</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>968488</t>
+          <t>944665</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -14663,12 +14663,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>18,04%</t>
+          <t>18,06%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>26,45%</t>
+          <t>25,8%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -14683,12 +14683,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>1099319</t>
+          <t>1103574</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>1443362</t>
+          <t>1432343</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -14698,12 +14698,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>15,44%</t>
+          <t>15,5%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>20,27%</t>
+          <t>20,11%</t>
         </is>
       </c>
     </row>
@@ -14726,12 +14726,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>2110312</t>
+          <t>2118230</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>2488974</t>
+          <t>2480845</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -14741,12 +14741,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>60,99%</t>
+          <t>61,22%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>71,94%</t>
+          <t>71,7%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -14761,12 +14761,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>2141329</t>
+          <t>2131766</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>2543774</t>
+          <t>2522759</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -14776,12 +14776,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>58,48%</t>
+          <t>58,22%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>69,47%</t>
+          <t>68,89%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -14796,12 +14796,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>4308895</t>
+          <t>4292537</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>4841701</t>
+          <t>4842420</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -14811,12 +14811,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>60,5%</t>
+          <t>60,27%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>67,99%</t>
+          <t>68,0%</t>
         </is>
       </c>
     </row>
@@ -14839,12 +14839,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>487616</t>
+          <t>481348</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>687813</t>
+          <t>681371</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -14854,12 +14854,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>14,09%</t>
+          <t>13,91%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>19,88%</t>
+          <t>19,69%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -14874,12 +14874,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>324923</t>
+          <t>325551</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>487851</t>
+          <t>487948</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -14889,12 +14889,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>8,87%</t>
+          <t>8,89%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>13,32%</t>
+          <t>13,33%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -14909,12 +14909,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>866842</t>
+          <t>860064</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>1118622</t>
+          <t>1116236</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -14924,12 +14924,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>12,17%</t>
+          <t>12,08%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>15,71%</t>
+          <t>15,67%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P40-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/P40-Habitat-trans_orig.xlsx
@@ -738,7 +738,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>4686</t>
+          <t>4760</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -753,7 +753,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>0,68%</t>
+          <t>0,69%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>2289</t>
+          <t>2343</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>12931</t>
+          <t>12653</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0,33%</t>
+          <t>0,34%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>1,88%</t>
+          <t>1,84%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>3134</t>
+          <t>3148</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>14144</t>
+          <t>14966</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -823,7 +823,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>1,02%</t>
+          <t>1,08%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>12238</t>
+          <t>12330</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>30251</t>
+          <t>29433</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>1,76%</t>
+          <t>1,78%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>4,36%</t>
+          <t>4,24%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>40525</t>
+          <t>39762</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>67645</t>
+          <t>67353</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>5,89%</t>
+          <t>5,78%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>9,83%</t>
+          <t>9,78%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>57694</t>
+          <t>58136</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>90452</t>
+          <t>90206</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>4,17%</t>
+          <t>4,21%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>6,54%</t>
+          <t>6,53%</t>
         </is>
       </c>
     </row>
@@ -959,12 +959,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>84346</t>
+          <t>82358</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>121850</t>
+          <t>119785</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -974,12 +974,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>12,15%</t>
+          <t>11,87%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>17,56%</t>
+          <t>17,26%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -994,12 +994,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>112422</t>
+          <t>114542</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>155602</t>
+          <t>154775</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1009,12 +1009,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>16,33%</t>
+          <t>16,64%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>22,61%</t>
+          <t>22,48%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1029,12 +1029,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>207817</t>
+          <t>207948</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>264727</t>
+          <t>261836</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1044,12 +1044,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>15,03%</t>
+          <t>15,04%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>19,15%</t>
+          <t>18,94%</t>
         </is>
       </c>
     </row>
@@ -1072,12 +1072,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>423515</t>
+          <t>424985</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>474253</t>
+          <t>473886</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1087,12 +1087,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>61,02%</t>
+          <t>61,24%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>68,33%</t>
+          <t>68,28%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1107,12 +1107,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>380164</t>
+          <t>382046</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>432535</t>
+          <t>430248</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1122,12 +1122,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>55,23%</t>
+          <t>55,5%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>62,84%</t>
+          <t>62,5%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1142,12 +1142,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>820661</t>
+          <t>823301</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>891125</t>
+          <t>893235</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1157,12 +1157,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>59,37%</t>
+          <t>59,56%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>64,46%</t>
+          <t>64,62%</t>
         </is>
       </c>
     </row>
@@ -1185,12 +1185,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>102528</t>
+          <t>104476</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>143638</t>
+          <t>143507</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1200,12 +1200,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>14,77%</t>
+          <t>15,05%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>20,7%</t>
+          <t>20,68%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1220,12 +1220,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>73474</t>
+          <t>73164</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>108568</t>
+          <t>107839</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1235,12 +1235,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>10,67%</t>
+          <t>10,63%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>15,77%</t>
+          <t>15,67%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1255,12 +1255,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>186097</t>
+          <t>183879</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>241274</t>
+          <t>238219</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1270,12 +1270,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>13,46%</t>
+          <t>13,3%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>17,45%</t>
+          <t>17,23%</t>
         </is>
       </c>
     </row>
@@ -1420,7 +1420,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>8960</t>
+          <t>9788</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1435,7 +1435,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>0,93%</t>
+          <t>1,02%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1455,7 +1455,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>6469</t>
+          <t>7618</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1470,7 +1470,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>0,67%</t>
+          <t>0,79%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1485,12 +1485,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>1155</t>
+          <t>1159</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>12331</t>
+          <t>11606</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1505,7 +1505,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>0,64%</t>
+          <t>0,6%</t>
         </is>
       </c>
     </row>
@@ -1528,12 +1528,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>13217</t>
+          <t>12963</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>32126</t>
+          <t>31270</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1543,12 +1543,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>1,38%</t>
+          <t>1,35%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>3,34%</t>
+          <t>3,25%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1563,12 +1563,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>33795</t>
+          <t>33082</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>60714</t>
+          <t>60487</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1578,12 +1578,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>3,49%</t>
+          <t>3,42%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>6,27%</t>
+          <t>6,25%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1598,12 +1598,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>51257</t>
+          <t>51231</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>84679</t>
+          <t>83959</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1618,7 +1618,7 @@
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>4,39%</t>
+          <t>4,35%</t>
         </is>
       </c>
     </row>
@@ -1641,12 +1641,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>105168</t>
+          <t>104483</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>147206</t>
+          <t>145198</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1656,12 +1656,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>10,95%</t>
+          <t>10,87%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>15,32%</t>
+          <t>15,11%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1676,12 +1676,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>238432</t>
+          <t>240011</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>295286</t>
+          <t>297966</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1691,12 +1691,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>24,62%</t>
+          <t>24,78%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>30,49%</t>
+          <t>30,77%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1711,12 +1711,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>358519</t>
+          <t>356389</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>430178</t>
+          <t>426571</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1726,12 +1726,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>18,58%</t>
+          <t>18,47%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>22,3%</t>
+          <t>22,11%</t>
         </is>
       </c>
     </row>
@@ -1754,12 +1754,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>587565</t>
+          <t>587792</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>648416</t>
+          <t>648042</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1769,12 +1769,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>61,15%</t>
+          <t>61,18%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>67,49%</t>
+          <t>67,45%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1789,12 +1789,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>503107</t>
+          <t>507033</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>569340</t>
+          <t>570400</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1804,12 +1804,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>51,95%</t>
+          <t>52,36%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>58,79%</t>
+          <t>58,9%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1824,12 +1824,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1112556</t>
+          <t>1109881</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>1195490</t>
+          <t>1199071</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1839,12 +1839,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>57,67%</t>
+          <t>57,53%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>61,97%</t>
+          <t>62,15%</t>
         </is>
       </c>
     </row>
@@ -1867,12 +1867,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>169881</t>
+          <t>168874</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>222990</t>
+          <t>224837</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1882,12 +1882,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>17,68%</t>
+          <t>17,58%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>23,21%</t>
+          <t>23,4%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1902,12 +1902,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>97198</t>
+          <t>96127</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>139098</t>
+          <t>136872</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1917,12 +1917,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>10,04%</t>
+          <t>9,93%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>14,36%</t>
+          <t>14,13%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1937,12 +1937,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>280121</t>
+          <t>276797</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>346001</t>
+          <t>345753</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1952,12 +1952,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>14,52%</t>
+          <t>14,35%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>17,93%</t>
+          <t>17,92%</t>
         </is>
       </c>
     </row>
@@ -2102,7 +2102,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>6130</t>
+          <t>6075</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2132,12 +2132,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>956</t>
+          <t>937</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>10726</t>
+          <t>11337</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2152,7 +2152,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>1,57%</t>
+          <t>1,66%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2167,12 +2167,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>2626</t>
+          <t>2172</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>14096</t>
+          <t>12987</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2182,12 +2182,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,19%</t>
+          <t>0,16%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>1,04%</t>
+          <t>0,96%</t>
         </is>
       </c>
     </row>
@@ -2210,12 +2210,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>4632</t>
+          <t>4831</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>19034</t>
+          <t>19117</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2225,12 +2225,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0,68%</t>
+          <t>0,71%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>2,81%</t>
+          <t>2,82%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2245,12 +2245,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>18868</t>
+          <t>19339</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>39934</t>
+          <t>40537</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2260,12 +2260,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>2,77%</t>
+          <t>2,84%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>5,85%</t>
+          <t>5,94%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2280,12 +2280,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>27234</t>
+          <t>27285</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>52950</t>
+          <t>51916</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2295,12 +2295,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>2,01%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>3,89%</t>
+          <t>3,82%</t>
         </is>
       </c>
     </row>
@@ -2323,12 +2323,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>74397</t>
+          <t>72804</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>109232</t>
+          <t>108348</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2338,12 +2338,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>10,98%</t>
+          <t>10,74%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>16,12%</t>
+          <t>15,99%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2358,12 +2358,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>115034</t>
+          <t>117449</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>157181</t>
+          <t>155256</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2373,12 +2373,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>16,87%</t>
+          <t>17,22%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>23,05%</t>
+          <t>22,76%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2393,12 +2393,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>200368</t>
+          <t>200833</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>253113</t>
+          <t>254893</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2408,12 +2408,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>14,74%</t>
+          <t>14,77%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>18,62%</t>
+          <t>18,75%</t>
         </is>
       </c>
     </row>
@@ -2436,12 +2436,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>415669</t>
+          <t>417854</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>466456</t>
+          <t>469799</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2451,12 +2451,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>61,35%</t>
+          <t>61,67%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>68,84%</t>
+          <t>69,34%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2471,12 +2471,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>394096</t>
+          <t>398940</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>444556</t>
+          <t>445944</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2486,12 +2486,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>57,78%</t>
+          <t>58,49%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>65,18%</t>
+          <t>65,38%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2506,12 +2506,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>827871</t>
+          <t>828427</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>899136</t>
+          <t>901638</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2521,12 +2521,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>60,89%</t>
+          <t>60,93%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>66,13%</t>
+          <t>66,32%</t>
         </is>
       </c>
     </row>
@@ -2549,12 +2549,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>112094</t>
+          <t>108941</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>154385</t>
+          <t>152109</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2564,12 +2564,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>16,54%</t>
+          <t>16,08%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>22,79%</t>
+          <t>22,45%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2584,12 +2584,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>76288</t>
+          <t>77845</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>112959</t>
+          <t>112159</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2599,12 +2599,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>11,19%</t>
+          <t>11,41%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>16,56%</t>
+          <t>16,44%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2619,12 +2619,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>198910</t>
+          <t>198407</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>254044</t>
+          <t>250620</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2634,12 +2634,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>14,63%</t>
+          <t>14,59%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>18,68%</t>
+          <t>18,43%</t>
         </is>
       </c>
     </row>
@@ -2784,7 +2784,7 @@
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>6075</t>
+          <t>6049</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2799,7 +2799,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>0,65%</t>
+          <t>0,64%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2814,12 +2814,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>2977</t>
+          <t>3056</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>13992</t>
+          <t>14234</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2834,7 +2834,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>1,35%</t>
+          <t>1,37%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2849,12 +2849,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>3859</t>
+          <t>4007</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>15987</t>
+          <t>16790</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2864,12 +2864,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>0,19%</t>
+          <t>0,2%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>0,81%</t>
+          <t>0,85%</t>
         </is>
       </c>
     </row>
@@ -2892,12 +2892,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>11176</t>
+          <t>11224</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>27073</t>
+          <t>26770</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2912,7 +2912,7 @@
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>2,88%</t>
+          <t>2,84%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2927,12 +2927,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>36905</t>
+          <t>35911</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>64848</t>
+          <t>63203</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2942,12 +2942,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>3,55%</t>
+          <t>3,46%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>6,24%</t>
+          <t>6,09%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2962,12 +2962,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>52565</t>
+          <t>52322</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>81987</t>
+          <t>84547</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2977,12 +2977,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>2,65%</t>
+          <t>2,64%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>4,14%</t>
+          <t>4,27%</t>
         </is>
       </c>
     </row>
@@ -3005,12 +3005,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>110621</t>
+          <t>110042</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>151735</t>
+          <t>150180</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3020,12 +3020,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>11,75%</t>
+          <t>11,69%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>16,12%</t>
+          <t>15,95%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3040,12 +3040,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>204675</t>
+          <t>207104</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>261133</t>
+          <t>257436</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3055,12 +3055,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>19,71%</t>
+          <t>19,94%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>25,14%</t>
+          <t>24,79%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3075,12 +3075,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>329352</t>
+          <t>329401</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>396946</t>
+          <t>399960</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3090,12 +3090,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>16,63%</t>
+          <t>16,64%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>20,05%</t>
+          <t>20,2%</t>
         </is>
       </c>
     </row>
@@ -3118,12 +3118,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>562687</t>
+          <t>565214</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>621449</t>
+          <t>623556</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3133,12 +3133,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>59,78%</t>
+          <t>60,04%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>66,02%</t>
+          <t>66,24%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3153,12 +3153,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>542397</t>
+          <t>540858</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>604605</t>
+          <t>602289</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3168,12 +3168,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>52,22%</t>
+          <t>52,08%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>58,21%</t>
+          <t>57,99%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3188,12 +3188,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>1121694</t>
+          <t>1121326</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>1212143</t>
+          <t>1206724</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3203,12 +3203,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>56,65%</t>
+          <t>56,63%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>61,22%</t>
+          <t>60,95%</t>
         </is>
       </c>
     </row>
@@ -3231,12 +3231,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>175074</t>
+          <t>174147</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>223496</t>
+          <t>222464</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3246,12 +3246,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>18,6%</t>
+          <t>18,5%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>23,74%</t>
+          <t>23,63%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3266,12 +3266,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>154591</t>
+          <t>153068</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>203802</t>
+          <t>205046</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3281,12 +3281,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>14,88%</t>
+          <t>14,74%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>19,62%</t>
+          <t>19,74%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3301,12 +3301,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>338651</t>
+          <t>340084</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>410573</t>
+          <t>410263</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3316,12 +3316,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>17,1%</t>
+          <t>17,18%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>20,74%</t>
+          <t>20,72%</t>
         </is>
       </c>
     </row>
@@ -3461,12 +3461,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>2832</t>
+          <t>2668</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>14841</t>
+          <t>14275</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3476,12 +3476,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>0,09%</t>
+          <t>0,08%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>0,45%</t>
+          <t>0,44%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3496,12 +3496,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>12274</t>
+          <t>12715</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>31298</t>
+          <t>31282</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3511,7 +3511,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>0,36%</t>
+          <t>0,38%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3531,12 +3531,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>18369</t>
+          <t>18029</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>38536</t>
+          <t>38689</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3546,7 +3546,7 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>0,28%</t>
+          <t>0,27%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
@@ -3574,12 +3574,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>55172</t>
+          <t>55387</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>87185</t>
+          <t>86736</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3594,7 +3594,7 @@
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>2,66%</t>
+          <t>2,65%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3609,12 +3609,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>150267</t>
+          <t>151658</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>201652</t>
+          <t>202130</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3624,12 +3624,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>4,45%</t>
+          <t>4,49%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>5,97%</t>
+          <t>5,98%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3644,12 +3644,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>213008</t>
+          <t>215023</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>276857</t>
+          <t>273709</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3659,12 +3659,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>3,2%</t>
+          <t>3,23%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>4,16%</t>
+          <t>4,12%</t>
         </is>
       </c>
     </row>
@@ -3687,12 +3687,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>408310</t>
+          <t>408113</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>486530</t>
+          <t>487196</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3707,7 +3707,7 @@
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>14,86%</t>
+          <t>14,88%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3722,12 +3722,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>719836</t>
+          <t>718112</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>818788</t>
+          <t>820301</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3737,12 +3737,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>21,31%</t>
+          <t>21,26%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>24,24%</t>
+          <t>24,29%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3757,12 +3757,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>1158393</t>
+          <t>1149989</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>1276432</t>
+          <t>1280183</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3772,12 +3772,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>17,42%</t>
+          <t>17,29%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>19,19%</t>
+          <t>19,25%</t>
         </is>
       </c>
     </row>
@@ -3800,12 +3800,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>2048100</t>
+          <t>2052187</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>2157650</t>
+          <t>2159173</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -3815,12 +3815,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>62,56%</t>
+          <t>62,69%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>65,91%</t>
+          <t>65,95%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -3835,12 +3835,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>1876910</t>
+          <t>1885894</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>1993177</t>
+          <t>1996888</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -3850,12 +3850,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>55,57%</t>
+          <t>55,84%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>59,01%</t>
+          <t>59,12%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3870,12 +3870,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>3967181</t>
+          <t>3960798</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>4121434</t>
+          <t>4122734</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -3885,12 +3885,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>59,65%</t>
+          <t>59,55%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>61,97%</t>
+          <t>61,99%</t>
         </is>
       </c>
     </row>
@@ -3913,12 +3913,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>600617</t>
+          <t>603049</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>698092</t>
+          <t>692888</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -3928,12 +3928,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>18,35%</t>
+          <t>18,42%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>21,32%</t>
+          <t>21,17%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3948,12 +3948,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>438108</t>
+          <t>437534</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>520091</t>
+          <t>520380</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -3963,12 +3963,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>12,97%</t>
+          <t>12,95%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>15,4%</t>
+          <t>15,41%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3983,12 +3983,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>1066689</t>
+          <t>1060892</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>1187120</t>
+          <t>1187191</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -3998,7 +3998,7 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>16,04%</t>
+          <t>15,95%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
@@ -4380,7 +4380,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>7561</t>
+          <t>7528</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4410,12 +4410,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>1938</t>
+          <t>1962</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>10931</t>
+          <t>11232</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4430,7 +4430,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>1,58%</t>
+          <t>1,62%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4445,12 +4445,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>3070</t>
+          <t>3049</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>14082</t>
+          <t>14491</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4465,7 +4465,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>1,01%</t>
+          <t>1,04%</t>
         </is>
       </c>
     </row>
@@ -4488,12 +4488,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>11355</t>
+          <t>10938</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>29266</t>
+          <t>27961</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4503,12 +4503,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>1,63%</t>
+          <t>1,57%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>4,19%</t>
+          <t>4,01%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4523,12 +4523,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>27218</t>
+          <t>25648</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>50405</t>
+          <t>50959</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4538,12 +4538,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>3,93%</t>
+          <t>3,7%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>7,27%</t>
+          <t>7,35%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4558,12 +4558,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>42703</t>
+          <t>42252</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>71643</t>
+          <t>72721</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4573,12 +4573,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>3,07%</t>
+          <t>3,04%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>5,15%</t>
+          <t>5,23%</t>
         </is>
       </c>
     </row>
@@ -4601,12 +4601,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>90754</t>
+          <t>90318</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>129352</t>
+          <t>131303</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -4616,12 +4616,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>13,01%</t>
+          <t>12,94%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>18,54%</t>
+          <t>18,82%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -4636,12 +4636,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>128203</t>
+          <t>127357</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>171166</t>
+          <t>171947</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -4651,12 +4651,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>18,5%</t>
+          <t>18,38%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>24,7%</t>
+          <t>24,82%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -4671,12 +4671,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>229764</t>
+          <t>229122</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>287479</t>
+          <t>287552</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -4686,12 +4686,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>16,52%</t>
+          <t>16,48%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>20,67%</t>
+          <t>20,68%</t>
         </is>
       </c>
     </row>
@@ -4714,12 +4714,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>387818</t>
+          <t>387103</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>439552</t>
+          <t>440440</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4729,12 +4729,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>55,58%</t>
+          <t>55,47%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>62,99%</t>
+          <t>63,12%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4749,12 +4749,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>379466</t>
+          <t>377892</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>431235</t>
+          <t>431379</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4764,12 +4764,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>54,77%</t>
+          <t>54,54%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>62,24%</t>
+          <t>62,26%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4784,12 +4784,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>782301</t>
+          <t>780460</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>855831</t>
+          <t>850373</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4799,12 +4799,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>56,25%</t>
+          <t>56,12%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>61,54%</t>
+          <t>61,15%</t>
         </is>
       </c>
     </row>
@@ -4827,12 +4827,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>133155</t>
+          <t>132469</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>176794</t>
+          <t>176940</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4842,12 +4842,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>19,08%</t>
+          <t>18,98%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>25,34%</t>
+          <t>25,36%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4862,12 +4862,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>80968</t>
+          <t>80298</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>119209</t>
+          <t>116557</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4877,12 +4877,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>11,69%</t>
+          <t>11,59%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>17,2%</t>
+          <t>16,82%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4897,12 +4897,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>222815</t>
+          <t>224921</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>282131</t>
+          <t>282255</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4912,12 +4912,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>16,02%</t>
+          <t>16,17%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>20,29%</t>
+          <t>20,3%</t>
         </is>
       </c>
     </row>
@@ -5057,12 +5057,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>932</t>
+          <t>933</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>8563</t>
+          <t>9049</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5077,7 +5077,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>0,85%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5092,12 +5092,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>2100</t>
+          <t>2073</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>12021</t>
+          <t>11990</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -5127,12 +5127,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>4085</t>
+          <t>3443</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>17023</t>
+          <t>16651</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5142,12 +5142,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,2%</t>
+          <t>0,17%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>0,84%</t>
+          <t>0,82%</t>
         </is>
       </c>
     </row>
@@ -5170,12 +5170,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>13081</t>
+          <t>12988</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>32182</t>
+          <t>32752</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -5185,12 +5185,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>1,29%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>3,2%</t>
+          <t>3,26%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -5205,12 +5205,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>31138</t>
+          <t>30379</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>56211</t>
+          <t>55951</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -5220,12 +5220,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>3,03%</t>
+          <t>2,96%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>5,47%</t>
+          <t>5,44%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -5240,12 +5240,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>47596</t>
+          <t>47568</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>80419</t>
+          <t>79809</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -5260,7 +5260,7 @@
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>3,96%</t>
+          <t>3,93%</t>
         </is>
       </c>
     </row>
@@ -5283,12 +5283,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>117897</t>
+          <t>117841</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>164672</t>
+          <t>163822</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -5298,12 +5298,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>11,73%</t>
+          <t>11,72%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>16,38%</t>
+          <t>16,29%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -5318,12 +5318,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>196356</t>
+          <t>198580</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>250863</t>
+          <t>252783</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -5333,12 +5333,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>19,1%</t>
+          <t>19,32%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>24,41%</t>
+          <t>24,59%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -5353,12 +5353,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>328755</t>
+          <t>329095</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>399525</t>
+          <t>403725</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -5368,12 +5368,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>16,17%</t>
+          <t>16,19%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>19,65%</t>
+          <t>19,86%</t>
         </is>
       </c>
     </row>
@@ -5396,12 +5396,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>607426</t>
+          <t>608452</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>671600</t>
+          <t>669784</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5411,12 +5411,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>60,42%</t>
+          <t>60,52%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>66,8%</t>
+          <t>66,62%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5431,12 +5431,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>590840</t>
+          <t>588241</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>653875</t>
+          <t>654195</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5446,12 +5446,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>57,48%</t>
+          <t>57,23%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>63,61%</t>
+          <t>63,65%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5466,12 +5466,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1213245</t>
+          <t>1219280</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>1305264</t>
+          <t>1317180</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5481,12 +5481,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>59,67%</t>
+          <t>59,97%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>64,19%</t>
+          <t>64,78%</t>
         </is>
       </c>
     </row>
@@ -5509,12 +5509,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>176104</t>
+          <t>176679</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>229431</t>
+          <t>229398</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5524,7 +5524,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>17,52%</t>
+          <t>17,57%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -5544,12 +5544,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>112067</t>
+          <t>112042</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>157196</t>
+          <t>156580</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5564,7 +5564,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>15,29%</t>
+          <t>15,23%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5579,12 +5579,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>300336</t>
+          <t>297153</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>370450</t>
+          <t>363984</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5594,12 +5594,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>14,77%</t>
+          <t>14,61%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>18,22%</t>
+          <t>17,9%</t>
         </is>
       </c>
     </row>
@@ -5744,7 +5744,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>5039</t>
+          <t>5172</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5759,7 +5759,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>0,68%</t>
+          <t>0,69%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5774,12 +5774,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>3996</t>
+          <t>3987</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>15960</t>
+          <t>15876</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5794,7 +5794,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>2,07%</t>
+          <t>2,06%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5809,12 +5809,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>4270</t>
+          <t>4315</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>17742</t>
+          <t>17593</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5829,7 +5829,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>1,17%</t>
+          <t>1,16%</t>
         </is>
       </c>
     </row>
@@ -5852,12 +5852,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>7428</t>
+          <t>7488</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>26332</t>
+          <t>25871</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5867,12 +5867,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>1,01%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>3,54%</t>
+          <t>3,47%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5887,12 +5887,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>22746</t>
+          <t>23769</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>48509</t>
+          <t>48910</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5902,12 +5902,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>2,95%</t>
+          <t>3,08%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>6,28%</t>
+          <t>6,33%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5922,12 +5922,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>35505</t>
+          <t>34513</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>64782</t>
+          <t>65593</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5937,12 +5937,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>2,34%</t>
+          <t>2,28%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>4,27%</t>
+          <t>4,32%</t>
         </is>
       </c>
     </row>
@@ -5965,12 +5965,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>82090</t>
+          <t>83010</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>123775</t>
+          <t>123132</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -5980,12 +5980,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>11,02%</t>
+          <t>11,15%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>16,62%</t>
+          <t>16,53%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -6000,12 +6000,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>143131</t>
+          <t>142233</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>191030</t>
+          <t>191260</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -6015,12 +6015,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>18,54%</t>
+          <t>18,42%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>24,74%</t>
+          <t>24,77%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -6035,12 +6035,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>236572</t>
+          <t>232503</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>299250</t>
+          <t>297021</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -6050,12 +6050,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>15,6%</t>
+          <t>15,33%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>19,73%</t>
+          <t>19,58%</t>
         </is>
       </c>
     </row>
@@ -6078,12 +6078,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>400062</t>
+          <t>398559</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>456859</t>
+          <t>456017</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -6093,12 +6093,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>53,72%</t>
+          <t>53,51%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>61,34%</t>
+          <t>61,23%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -6113,12 +6113,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>405213</t>
+          <t>406608</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>461360</t>
+          <t>462655</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -6128,12 +6128,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>52,48%</t>
+          <t>52,66%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>59,75%</t>
+          <t>59,91%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -6148,12 +6148,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>819667</t>
+          <t>817679</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>896891</t>
+          <t>899808</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -6163,12 +6163,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>54,03%</t>
+          <t>53,9%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>59,12%</t>
+          <t>59,32%</t>
         </is>
       </c>
     </row>
@@ -6191,12 +6191,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>177043</t>
+          <t>175611</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>228613</t>
+          <t>224554</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -6206,12 +6206,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>23,77%</t>
+          <t>23,58%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>30,7%</t>
+          <t>30,15%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -6226,12 +6226,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>111635</t>
+          <t>109921</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>154769</t>
+          <t>154528</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -6241,12 +6241,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>14,46%</t>
+          <t>14,23%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>20,04%</t>
+          <t>20,01%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -6261,12 +6261,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>300422</t>
+          <t>299148</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>367997</t>
+          <t>367025</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -6276,12 +6276,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>19,8%</t>
+          <t>19,72%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>24,26%</t>
+          <t>24,19%</t>
         </is>
       </c>
     </row>
@@ -6421,12 +6421,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>933</t>
+          <t>934</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>9163</t>
+          <t>9388</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -6441,7 +6441,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>0,98%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -6456,12 +6456,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>4815</t>
+          <t>4620</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>19037</t>
+          <t>18496</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -6471,12 +6471,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>0,46%</t>
+          <t>0,44%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>1,83%</t>
+          <t>1,77%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -6491,12 +6491,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>6910</t>
+          <t>6884</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>23494</t>
+          <t>23086</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -6511,7 +6511,7 @@
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>1,19%</t>
+          <t>1,17%</t>
         </is>
       </c>
     </row>
@@ -6534,12 +6534,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>16017</t>
+          <t>15258</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>37695</t>
+          <t>38222</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -6549,12 +6549,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>1,71%</t>
+          <t>1,63%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>4,03%</t>
+          <t>4,09%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -6569,12 +6569,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>36113</t>
+          <t>36698</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>64619</t>
+          <t>64294</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -6584,12 +6584,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>3,47%</t>
+          <t>3,52%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>6,2%</t>
+          <t>6,17%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -6604,12 +6604,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>57220</t>
+          <t>58500</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>93921</t>
+          <t>95281</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -6619,12 +6619,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>2,89%</t>
+          <t>2,96%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>4,75%</t>
+          <t>4,82%</t>
         </is>
       </c>
     </row>
@@ -6647,12 +6647,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>113830</t>
+          <t>113809</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>154987</t>
+          <t>155846</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -6667,7 +6667,7 @@
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>16,59%</t>
+          <t>16,68%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -6682,12 +6682,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>199316</t>
+          <t>200289</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>255399</t>
+          <t>251469</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -6697,12 +6697,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>19,13%</t>
+          <t>19,22%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>24,51%</t>
+          <t>24,13%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -6717,12 +6717,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>321942</t>
+          <t>325799</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>390389</t>
+          <t>393831</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -6732,12 +6732,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>16,29%</t>
+          <t>16,48%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>19,75%</t>
+          <t>19,92%</t>
         </is>
       </c>
     </row>
@@ -6760,12 +6760,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>579275</t>
+          <t>576979</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>637720</t>
+          <t>637082</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6775,12 +6775,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>61,99%</t>
+          <t>61,75%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>68,25%</t>
+          <t>68,18%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6795,12 +6795,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>635313</t>
+          <t>635902</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>697586</t>
+          <t>698962</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6810,12 +6810,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>60,96%</t>
+          <t>61,02%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>66,94%</t>
+          <t>67,07%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6830,12 +6830,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>1226218</t>
+          <t>1228511</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>1312803</t>
+          <t>1315205</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6845,12 +6845,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>62,04%</t>
+          <t>62,15%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>66,42%</t>
+          <t>66,54%</t>
         </is>
       </c>
     </row>
@@ -6873,12 +6873,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>142839</t>
+          <t>143944</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>189154</t>
+          <t>190843</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6888,12 +6888,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>15,29%</t>
+          <t>15,4%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>20,24%</t>
+          <t>20,42%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6908,12 +6908,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>74140</t>
+          <t>76288</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>112147</t>
+          <t>112228</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6923,12 +6923,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>7,11%</t>
+          <t>7,32%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>10,76%</t>
+          <t>10,77%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6943,12 +6943,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>230681</t>
+          <t>229130</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>289380</t>
+          <t>290115</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6958,12 +6958,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>11,67%</t>
+          <t>11,59%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>14,64%</t>
+          <t>14,68%</t>
         </is>
       </c>
     </row>
@@ -7103,12 +7103,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>4469</t>
+          <t>4376</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>17684</t>
+          <t>16808</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -7123,7 +7123,7 @@
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>0,52%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -7138,12 +7138,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>19862</t>
+          <t>19604</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>41795</t>
+          <t>42315</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -7153,39 +7153,39 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
+          <t>0,55%</t>
+        </is>
+      </c>
+      <c r="P28" s="2" t="inlineStr">
+        <is>
+          <t>1,2%</t>
+        </is>
+      </c>
+      <c r="Q28" s="2" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="R28" s="2" t="inlineStr">
+        <is>
+          <t>38408</t>
+        </is>
+      </c>
+      <c r="S28" s="2" t="inlineStr">
+        <is>
+          <t>27003</t>
+        </is>
+      </c>
+      <c r="T28" s="2" t="inlineStr">
+        <is>
+          <t>53664</t>
+        </is>
+      </c>
+      <c r="U28" s="2" t="inlineStr">
+        <is>
           <t>0,56%</t>
         </is>
       </c>
-      <c r="P28" s="2" t="inlineStr">
-        <is>
-          <t>1,18%</t>
-        </is>
-      </c>
-      <c r="Q28" s="2" t="inlineStr">
-        <is>
-          <t>36</t>
-        </is>
-      </c>
-      <c r="R28" s="2" t="inlineStr">
-        <is>
-          <t>38408</t>
-        </is>
-      </c>
-      <c r="S28" s="2" t="inlineStr">
-        <is>
-          <t>26642</t>
-        </is>
-      </c>
-      <c r="T28" s="2" t="inlineStr">
-        <is>
-          <t>51861</t>
-        </is>
-      </c>
-      <c r="U28" s="2" t="inlineStr">
-        <is>
-          <t>0,56%</t>
-        </is>
-      </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
           <t>0,39%</t>
@@ -7193,7 +7193,7 @@
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>0,75%</t>
+          <t>0,78%</t>
         </is>
       </c>
     </row>
@@ -7216,12 +7216,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>62231</t>
+          <t>61238</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>100909</t>
+          <t>97322</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -7231,12 +7231,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>1,84%</t>
+          <t>1,81%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>2,98%</t>
+          <t>2,88%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -7251,12 +7251,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>138437</t>
+          <t>138031</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>189723</t>
+          <t>190277</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -7266,12 +7266,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>3,92%</t>
+          <t>3,9%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>5,37%</t>
+          <t>5,38%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -7286,12 +7286,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>209932</t>
+          <t>210297</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>274056</t>
+          <t>277016</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -7301,12 +7301,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>3,03%</t>
+          <t>3,04%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>3,96%</t>
+          <t>4,0%</t>
         </is>
       </c>
     </row>
@@ -7329,12 +7329,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>442474</t>
+          <t>439492</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>529869</t>
+          <t>530210</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -7344,12 +7344,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>13,08%</t>
+          <t>12,99%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>15,67%</t>
+          <t>15,68%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -7364,12 +7364,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>713135</t>
+          <t>711168</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>811339</t>
+          <t>810086</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -7379,12 +7379,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>20,17%</t>
+          <t>20,12%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>22,95%</t>
+          <t>22,92%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -7399,12 +7399,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>1176775</t>
+          <t>1174494</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>1310390</t>
+          <t>1309634</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -7414,12 +7414,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>17,01%</t>
+          <t>16,98%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>18,94%</t>
+          <t>18,93%</t>
         </is>
       </c>
     </row>
@@ -7442,12 +7442,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>2028477</t>
+          <t>2028992</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>2147727</t>
+          <t>2146023</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -7457,12 +7457,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>59,97%</t>
+          <t>59,99%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>63,5%</t>
+          <t>63,45%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -7477,12 +7477,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>2062875</t>
+          <t>2066426</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>2185424</t>
+          <t>2181685</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -7492,12 +7492,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>58,35%</t>
+          <t>58,45%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>61,82%</t>
+          <t>61,71%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -7512,12 +7512,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>4134438</t>
+          <t>4123602</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>4296547</t>
+          <t>4296834</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -7527,7 +7527,7 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>59,77%</t>
+          <t>59,61%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
@@ -7555,12 +7555,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>674234</t>
+          <t>675439</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>771165</t>
+          <t>767853</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -7570,12 +7570,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>19,93%</t>
+          <t>19,97%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>22,8%</t>
+          <t>22,7%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -7590,12 +7590,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>416333</t>
+          <t>416883</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>497352</t>
+          <t>496046</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -7605,12 +7605,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>11,78%</t>
+          <t>11,79%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>14,07%</t>
+          <t>14,03%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -7625,12 +7625,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>1121460</t>
+          <t>1114917</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>1246274</t>
+          <t>1246139</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -7640,12 +7640,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>16,21%</t>
+          <t>16,12%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>18,02%</t>
+          <t>18,01%</t>
         </is>
       </c>
     </row>
@@ -8017,12 +8017,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>1721</t>
+          <t>1735</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>10235</t>
+          <t>10312</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -8037,7 +8037,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>1,53%</t>
+          <t>1,54%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -8057,7 +8057,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>7997</t>
+          <t>6313</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -8072,7 +8072,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>0,94%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -8087,12 +8087,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>2650</t>
+          <t>2712</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>12598</t>
+          <t>12800</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -8107,7 +8107,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>0,94%</t>
+          <t>0,96%</t>
         </is>
       </c>
     </row>
@@ -8130,12 +8130,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>9288</t>
+          <t>9262</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>25409</t>
+          <t>25161</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -8145,12 +8145,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>1,39%</t>
+          <t>1,38%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>3,79%</t>
+          <t>3,76%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -8165,12 +8165,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>31176</t>
+          <t>31690</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>57120</t>
+          <t>59312</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -8180,12 +8180,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>4,66%</t>
+          <t>4,74%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>8,54%</t>
+          <t>8,87%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -8200,12 +8200,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>45405</t>
+          <t>45547</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>75949</t>
+          <t>76475</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -8215,12 +8215,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>3,39%</t>
+          <t>3,4%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>5,68%</t>
+          <t>5,71%</t>
         </is>
       </c>
     </row>
@@ -8243,12 +8243,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>78220</t>
+          <t>78303</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>113469</t>
+          <t>113907</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -8258,12 +8258,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>11,68%</t>
+          <t>11,69%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>16,95%</t>
+          <t>17,01%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -8278,12 +8278,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>129150</t>
+          <t>128997</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>171717</t>
+          <t>170063</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -8293,12 +8293,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>19,32%</t>
+          <t>19,29%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>25,68%</t>
+          <t>25,44%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -8313,12 +8313,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>216972</t>
+          <t>216808</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>273680</t>
+          <t>274514</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -8328,12 +8328,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>16,21%</t>
+          <t>16,2%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>20,45%</t>
+          <t>20,51%</t>
         </is>
       </c>
     </row>
@@ -8356,12 +8356,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>354138</t>
+          <t>356965</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>405601</t>
+          <t>409732</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -8371,12 +8371,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>52,89%</t>
+          <t>53,31%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>60,57%</t>
+          <t>61,19%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -8391,12 +8391,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>311382</t>
+          <t>311625</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>363106</t>
+          <t>360128</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -8406,12 +8406,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>46,57%</t>
+          <t>46,61%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>54,31%</t>
+          <t>53,86%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -8426,12 +8426,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>683275</t>
+          <t>683444</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>753358</t>
+          <t>755516</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -8441,12 +8441,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>51,06%</t>
+          <t>51,07%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>56,3%</t>
+          <t>56,46%</t>
         </is>
       </c>
     </row>
@@ -8469,12 +8469,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>153605</t>
+          <t>150134</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>199107</t>
+          <t>196007</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -8484,12 +8484,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>22,94%</t>
+          <t>22,42%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>29,74%</t>
+          <t>29,27%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -8504,12 +8504,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>117473</t>
+          <t>118170</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>158846</t>
+          <t>156681</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -8519,12 +8519,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>17,57%</t>
+          <t>17,67%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>23,76%</t>
+          <t>23,43%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -8539,12 +8539,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>278741</t>
+          <t>279684</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>340062</t>
+          <t>338950</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -8554,12 +8554,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>20,83%</t>
+          <t>20,9%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>25,41%</t>
+          <t>25,33%</t>
         </is>
       </c>
     </row>
@@ -8704,7 +8704,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>4565</t>
+          <t>5250</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -8719,7 +8719,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>0,45%</t>
+          <t>0,52%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -8739,7 +8739,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>9467</t>
+          <t>9589</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -8754,7 +8754,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>0,92%</t>
+          <t>0,93%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -8769,12 +8769,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>1020</t>
+          <t>1250</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>10237</t>
+          <t>9609</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -8784,12 +8784,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,05%</t>
+          <t>0,06%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,47%</t>
         </is>
       </c>
     </row>
@@ -8812,12 +8812,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>13906</t>
+          <t>13833</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>31564</t>
+          <t>32157</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -8827,12 +8827,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>1,37%</t>
+          <t>1,36%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>3,1%</t>
+          <t>3,16%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -8847,12 +8847,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>22582</t>
+          <t>23244</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>48706</t>
+          <t>48608</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -8862,12 +8862,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>2,18%</t>
+          <t>2,25%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>4,71%</t>
+          <t>4,7%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -8882,12 +8882,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>40317</t>
+          <t>41667</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>72401</t>
+          <t>72372</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -8897,7 +8897,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>1,96%</t>
+          <t>2,03%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -8925,12 +8925,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>115892</t>
+          <t>114553</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>160288</t>
+          <t>159197</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -8940,12 +8940,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>11,38%</t>
+          <t>11,25%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>15,74%</t>
+          <t>15,63%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -8960,12 +8960,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>189227</t>
+          <t>190789</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>247278</t>
+          <t>246621</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -8975,12 +8975,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>18,3%</t>
+          <t>18,45%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>23,91%</t>
+          <t>23,85%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -8995,12 +8995,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>318909</t>
+          <t>317379</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>388529</t>
+          <t>387902</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -9010,12 +9010,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>15,54%</t>
+          <t>15,46%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>18,93%</t>
+          <t>18,9%</t>
         </is>
       </c>
     </row>
@@ -9038,12 +9038,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>568911</t>
+          <t>570479</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>635395</t>
+          <t>634362</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -9053,12 +9053,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>55,86%</t>
+          <t>56,01%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>62,38%</t>
+          <t>62,28%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -9073,12 +9073,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>570473</t>
+          <t>571135</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>639135</t>
+          <t>636528</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -9088,12 +9088,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>55,17%</t>
+          <t>55,23%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>61,81%</t>
+          <t>61,55%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -9108,12 +9108,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1156019</t>
+          <t>1160051</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>1255095</t>
+          <t>1253754</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -9123,12 +9123,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>56,32%</t>
+          <t>56,52%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>61,15%</t>
+          <t>61,08%</t>
         </is>
       </c>
     </row>
@@ -9151,12 +9151,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>229353</t>
+          <t>227936</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>288209</t>
+          <t>284554</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -9166,12 +9166,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>22,52%</t>
+          <t>22,38%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>28,3%</t>
+          <t>27,94%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -9186,12 +9186,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>150367</t>
+          <t>149867</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>198704</t>
+          <t>202136</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -9201,12 +9201,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>14,54%</t>
+          <t>14,49%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>19,22%</t>
+          <t>19,55%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -9221,12 +9221,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>395174</t>
+          <t>396281</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>472989</t>
+          <t>472941</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -9236,7 +9236,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>19,25%</t>
+          <t>19,31%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -9386,7 +9386,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>11121</t>
+          <t>12015</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -9401,7 +9401,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>1,47%</t>
+          <t>1,58%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -9416,12 +9416,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>3526</t>
+          <t>3584</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>16660</t>
+          <t>17647</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -9431,12 +9431,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0,45%</t>
+          <t>0,46%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>2,14%</t>
+          <t>2,27%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -9451,12 +9451,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>5280</t>
+          <t>5918</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>21172</t>
+          <t>21904</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -9466,12 +9466,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,34%</t>
+          <t>0,39%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>1,38%</t>
+          <t>1,43%</t>
         </is>
       </c>
     </row>
@@ -9494,12 +9494,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>9642</t>
+          <t>9713</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>25540</t>
+          <t>25703</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -9509,12 +9509,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>1,27%</t>
+          <t>1,28%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>3,37%</t>
+          <t>3,39%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -9529,12 +9529,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>23071</t>
+          <t>22003</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>46276</t>
+          <t>47587</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -9544,12 +9544,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>2,97%</t>
+          <t>2,83%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>5,95%</t>
+          <t>6,12%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -9564,12 +9564,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>35986</t>
+          <t>36750</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>67717</t>
+          <t>64777</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -9579,12 +9579,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>2,34%</t>
+          <t>2,39%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>4,41%</t>
+          <t>4,22%</t>
         </is>
       </c>
     </row>
@@ -9607,12 +9607,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>80786</t>
+          <t>80540</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>118230</t>
+          <t>119228</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -9622,12 +9622,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>10,65%</t>
+          <t>10,62%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>15,59%</t>
+          <t>15,72%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -9642,12 +9642,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>109216</t>
+          <t>108847</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>154388</t>
+          <t>154148</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -9657,12 +9657,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>14,05%</t>
+          <t>14,01%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>19,87%</t>
+          <t>19,84%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -9677,12 +9677,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>200784</t>
+          <t>202587</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>256399</t>
+          <t>257144</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -9692,12 +9692,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>13,08%</t>
+          <t>13,19%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>16,7%</t>
+          <t>16,75%</t>
         </is>
       </c>
     </row>
@@ -9720,12 +9720,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>421813</t>
+          <t>421606</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>477016</t>
+          <t>478375</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -9735,12 +9735,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>55,62%</t>
+          <t>55,59%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>62,9%</t>
+          <t>63,08%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -9755,12 +9755,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>412691</t>
+          <t>412240</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>469231</t>
+          <t>468993</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -9770,12 +9770,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>53,1%</t>
+          <t>53,05%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>60,38%</t>
+          <t>60,35%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -9790,12 +9790,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>843901</t>
+          <t>848036</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>925611</t>
+          <t>928897</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -9805,12 +9805,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>54,96%</t>
+          <t>55,23%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>60,28%</t>
+          <t>60,49%</t>
         </is>
       </c>
     </row>
@@ -9833,12 +9833,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>165419</t>
+          <t>165980</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>217150</t>
+          <t>218691</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -9848,12 +9848,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>21,81%</t>
+          <t>21,88%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>28,63%</t>
+          <t>28,84%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -9868,12 +9868,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>141910</t>
+          <t>143085</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>187185</t>
+          <t>187616</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -9883,12 +9883,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>18,26%</t>
+          <t>18,41%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>24,09%</t>
+          <t>24,14%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -9903,12 +9903,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>321495</t>
+          <t>324289</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>391117</t>
+          <t>390830</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -9918,12 +9918,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>20,94%</t>
+          <t>21,12%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>25,47%</t>
+          <t>25,45%</t>
         </is>
       </c>
     </row>
@@ -10068,7 +10068,7 @@
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>6356</t>
+          <t>6557</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -10083,7 +10083,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>0,69%</t>
+          <t>0,71%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -10098,12 +10098,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>3389</t>
+          <t>3319</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>16160</t>
+          <t>15692</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -10113,12 +10113,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>0,33%</t>
+          <t>0,32%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>1,56%</t>
+          <t>1,52%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -10133,12 +10133,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>5360</t>
+          <t>4306</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>18587</t>
+          <t>17980</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -10148,12 +10148,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>0,27%</t>
+          <t>0,22%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>0,95%</t>
+          <t>0,92%</t>
         </is>
       </c>
     </row>
@@ -10176,12 +10176,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>12384</t>
+          <t>12279</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>32303</t>
+          <t>31540</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -10191,12 +10191,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>1,34%</t>
+          <t>1,33%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>3,49%</t>
+          <t>3,4%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -10211,12 +10211,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>30023</t>
+          <t>30134</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>56355</t>
+          <t>58318</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -10226,12 +10226,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>2,9%</t>
+          <t>2,91%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>5,45%</t>
+          <t>5,64%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -10246,12 +10246,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>46189</t>
+          <t>47295</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>80633</t>
+          <t>79728</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -10261,12 +10261,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>2,36%</t>
+          <t>2,41%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>4,11%</t>
+          <t>4,07%</t>
         </is>
       </c>
     </row>
@@ -10289,12 +10289,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>106004</t>
+          <t>103946</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>144162</t>
+          <t>143657</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -10304,12 +10304,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>11,44%</t>
+          <t>11,22%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>15,56%</t>
+          <t>15,5%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -10324,12 +10324,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>184906</t>
+          <t>187137</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>242581</t>
+          <t>246199</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -10339,12 +10339,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>17,87%</t>
+          <t>18,09%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>23,45%</t>
+          <t>23,8%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -10359,12 +10359,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>301805</t>
+          <t>304159</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>371872</t>
+          <t>373115</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -10374,12 +10374,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>15,39%</t>
+          <t>15,51%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>18,96%</t>
+          <t>19,03%</t>
         </is>
       </c>
     </row>
@@ -10402,12 +10402,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>516389</t>
+          <t>517834</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>575801</t>
+          <t>574763</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -10417,12 +10417,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>55,72%</t>
+          <t>55,88%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>62,14%</t>
+          <t>62,02%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -10437,12 +10437,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>560239</t>
+          <t>556847</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>626508</t>
+          <t>625626</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -10452,12 +10452,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>54,16%</t>
+          <t>53,83%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>60,56%</t>
+          <t>60,48%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -10472,12 +10472,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>1087421</t>
+          <t>1092475</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>1179147</t>
+          <t>1180199</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -10487,12 +10487,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>55,45%</t>
+          <t>55,71%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>60,12%</t>
+          <t>60,18%</t>
         </is>
       </c>
     </row>
@@ -10515,12 +10515,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>205316</t>
+          <t>208943</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>258593</t>
+          <t>257097</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -10530,12 +10530,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>22,16%</t>
+          <t>22,55%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>27,91%</t>
+          <t>27,74%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -10550,12 +10550,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>156790</t>
+          <t>154913</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>203173</t>
+          <t>205180</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -10565,12 +10565,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>15,16%</t>
+          <t>14,98%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>19,64%</t>
+          <t>19,83%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -10585,12 +10585,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>376201</t>
+          <t>374342</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>448988</t>
+          <t>446849</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -10600,12 +10600,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>19,18%</t>
+          <t>19,09%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>22,89%</t>
+          <t>22,78%</t>
         </is>
       </c>
     </row>
@@ -10745,12 +10745,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>5192</t>
+          <t>5209</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>19122</t>
+          <t>19162</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -10780,12 +10780,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>12831</t>
+          <t>13430</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>32428</t>
+          <t>33439</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -10795,12 +10795,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>0,37%</t>
+          <t>0,38%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>0,92%</t>
+          <t>0,95%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -10815,12 +10815,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>21192</t>
+          <t>22475</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>44785</t>
+          <t>45479</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -10830,12 +10830,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>0,31%</t>
+          <t>0,33%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>0,65%</t>
+          <t>0,66%</t>
         </is>
       </c>
     </row>
@@ -10858,12 +10858,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>57787</t>
+          <t>59165</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>93125</t>
+          <t>94107</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -10873,12 +10873,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>1,71%</t>
+          <t>1,75%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>2,76%</t>
+          <t>2,79%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -10893,12 +10893,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>128500</t>
+          <t>124822</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>180626</t>
+          <t>178393</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -10908,12 +10908,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>3,66%</t>
+          <t>3,55%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>5,14%</t>
+          <t>5,08%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -10928,12 +10928,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>196374</t>
+          <t>197249</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>259414</t>
+          <t>260625</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -10943,12 +10943,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>2,85%</t>
+          <t>2,86%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>3,77%</t>
+          <t>3,78%</t>
         </is>
       </c>
     </row>
@@ -10971,12 +10971,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>416746</t>
+          <t>413983</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>497109</t>
+          <t>495856</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -10986,12 +10986,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>12,35%</t>
+          <t>12,27%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>14,74%</t>
+          <t>14,7%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -11006,12 +11006,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>660771</t>
+          <t>664411</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>766540</t>
+          <t>762677</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -11021,12 +11021,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>18,8%</t>
+          <t>18,91%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>21,81%</t>
+          <t>21,7%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -11041,12 +11041,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>1102679</t>
+          <t>1098503</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>1230578</t>
+          <t>1228311</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -11056,12 +11056,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>16,01%</t>
+          <t>15,95%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>17,87%</t>
+          <t>17,83%</t>
         </is>
       </c>
     </row>
@@ -11084,12 +11084,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>1922226</t>
+          <t>1918161</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>2037363</t>
+          <t>2037272</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -11099,7 +11099,7 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>56,99%</t>
+          <t>56,86%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
@@ -11119,12 +11119,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>1912047</t>
+          <t>1910223</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>2039684</t>
+          <t>2036495</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -11134,12 +11134,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>54,41%</t>
+          <t>54,36%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>58,04%</t>
+          <t>57,95%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -11154,12 +11154,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>3874916</t>
+          <t>3876922</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>4034836</t>
+          <t>4039031</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -11169,12 +11169,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>56,26%</t>
+          <t>56,29%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>58,58%</t>
+          <t>58,64%</t>
         </is>
       </c>
     </row>
@@ -11197,12 +11197,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>806633</t>
+          <t>798862</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>903410</t>
+          <t>904668</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -11212,12 +11212,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>23,91%</t>
+          <t>23,68%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>26,78%</t>
+          <t>26,82%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -11232,12 +11232,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>604596</t>
+          <t>611296</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>699330</t>
+          <t>704178</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -11247,12 +11247,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>17,2%</t>
+          <t>17,39%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>19,9%</t>
+          <t>20,04%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -11267,12 +11267,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>1444663</t>
+          <t>1442233</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>1579264</t>
+          <t>1584336</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -11282,12 +11282,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>20,98%</t>
+          <t>20,94%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>22,93%</t>
+          <t>23,0%</t>
         </is>
       </c>
     </row>
@@ -11654,17 +11654,17 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>7260</t>
+          <t>7878</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>3285</t>
+          <t>4234</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>13791</t>
+          <t>15913</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -11674,12 +11674,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,52%</t>
+          <t>0,61%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>2,17%</t>
+          <t>2,3%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -11689,17 +11689,17 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>10387</t>
+          <t>11289</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>6850</t>
+          <t>7499</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>15775</t>
+          <t>17159</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -11709,7 +11709,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>1,01%</t>
+          <t>1,02%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -11724,17 +11724,17 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>17647</t>
+          <t>19167</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>12219</t>
+          <t>12990</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>25521</t>
+          <t>27343</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -11744,12 +11744,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,93%</t>
+          <t>0,91%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>1,95%</t>
+          <t>1,92%</t>
         </is>
       </c>
     </row>
@@ -11767,32 +11767,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>29504</t>
+          <t>30750</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>22188</t>
+          <t>22660</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>39291</t>
+          <t>40677</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>4,64%</t>
+          <t>4,45%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>3,49%</t>
+          <t>3,28%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>6,18%</t>
+          <t>5,89%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -11802,32 +11802,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>47433</t>
+          <t>50795</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>39073</t>
+          <t>42117</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>57590</t>
+          <t>61601</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>7,02%</t>
+          <t>6,93%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>5,79%</t>
+          <t>5,75%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>8,53%</t>
+          <t>8,41%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -11837,32 +11837,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>76937</t>
+          <t>81545</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>65814</t>
+          <t>69365</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>90397</t>
+          <t>96127</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>5,87%</t>
+          <t>5,73%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>5,02%</t>
+          <t>4,87%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>6,9%</t>
+          <t>6,75%</t>
         </is>
       </c>
     </row>
@@ -11880,32 +11880,32 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>112502</t>
+          <t>120553</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>95618</t>
+          <t>101133</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>132862</t>
+          <t>140344</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>17,7%</t>
+          <t>17,45%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>15,05%</t>
+          <t>14,64%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>20,91%</t>
+          <t>20,32%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -11915,32 +11915,32 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>151389</t>
+          <t>161799</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>135637</t>
+          <t>145572</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>168037</t>
+          <t>181185</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>22,42%</t>
+          <t>22,08%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>20,08%</t>
+          <t>19,87%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>24,88%</t>
+          <t>24,73%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -11950,32 +11950,32 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>263892</t>
+          <t>282352</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>239525</t>
+          <t>256647</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>288632</t>
+          <t>309772</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>20,13%</t>
+          <t>19,84%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>18,27%</t>
+          <t>18,03%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>22,02%</t>
+          <t>21,76%</t>
         </is>
       </c>
     </row>
@@ -11993,32 +11993,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>396678</t>
+          <t>430706</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>368129</t>
+          <t>403139</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>422445</t>
+          <t>456159</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>62,43%</t>
+          <t>62,36%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>57,93%</t>
+          <t>58,37%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>66,48%</t>
+          <t>66,04%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -12028,32 +12028,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>402954</t>
+          <t>436758</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>383421</t>
+          <t>415215</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>421827</t>
+          <t>457967</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>59,66%</t>
+          <t>59,61%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>56,77%</t>
+          <t>56,67%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>62,46%</t>
+          <t>62,5%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -12063,32 +12063,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>799632</t>
+          <t>867463</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>762953</t>
+          <t>831838</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>834426</t>
+          <t>899689</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>61,0%</t>
+          <t>60,94%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>58,2%</t>
+          <t>58,44%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>63,66%</t>
+          <t>63,21%</t>
         </is>
       </c>
     </row>
@@ -12106,32 +12106,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>89496</t>
+          <t>100822</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>67501</t>
+          <t>79627</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>121849</t>
+          <t>129619</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>14,08%</t>
+          <t>14,6%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>10,62%</t>
+          <t>11,53%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>19,18%</t>
+          <t>18,77%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -12141,32 +12141,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>63207</t>
+          <t>72081</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>50690</t>
+          <t>58049</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>77019</t>
+          <t>89659</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>9,36%</t>
+          <t>9,84%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>7,51%</t>
+          <t>7,92%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>11,4%</t>
+          <t>12,24%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -12176,32 +12176,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>152703</t>
+          <t>172903</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>126840</t>
+          <t>145954</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>187036</t>
+          <t>202932</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>11,65%</t>
+          <t>12,15%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>9,68%</t>
+          <t>10,25%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>14,27%</t>
+          <t>14,26%</t>
         </is>
       </c>
     </row>
@@ -12219,17 +12219,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>635441</t>
+          <t>690710</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>635441</t>
+          <t>690710</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>635441</t>
+          <t>690710</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -12254,17 +12254,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>675370</t>
+          <t>732722</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>675370</t>
+          <t>732722</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>675370</t>
+          <t>732722</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -12289,17 +12289,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>1310811</t>
+          <t>1423431</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>1310811</t>
+          <t>1423431</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>1310811</t>
+          <t>1423431</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -12336,32 +12336,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>9757</t>
+          <t>10449</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>4788</t>
+          <t>5489</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>18195</t>
+          <t>18110</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>0,82%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,52%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>1,53%</t>
+          <t>1,73%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -12371,32 +12371,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>14233</t>
+          <t>15724</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>9588</t>
+          <t>10857</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>19956</t>
+          <t>22561</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>1,49%</t>
+          <t>1,47%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>1,01%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>2,08%</t>
+          <t>2,11%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -12406,32 +12406,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>23990</t>
+          <t>26172</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>14873</t>
+          <t>18939</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>33388</t>
+          <t>35288</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>1,12%</t>
+          <t>1,23%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,69%</t>
+          <t>0,89%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>1,55%</t>
+          <t>1,66%</t>
         </is>
       </c>
     </row>
@@ -12449,32 +12449,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>30493</t>
+          <t>33238</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>14921</t>
+          <t>24422</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>44327</t>
+          <t>45758</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>2,56%</t>
+          <t>3,17%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>1,25%</t>
+          <t>2,33%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>3,72%</t>
+          <t>4,36%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -12484,32 +12484,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>50399</t>
+          <t>54547</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>40971</t>
+          <t>44288</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>61258</t>
+          <t>66202</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>5,26%</t>
+          <t>5,09%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>4,28%</t>
+          <t>4,14%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>6,39%</t>
+          <t>6,18%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -12519,32 +12519,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>80892</t>
+          <t>87785</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>54579</t>
+          <t>73566</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>98463</t>
+          <t>103461</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>3,76%</t>
+          <t>4,14%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>2,54%</t>
+          <t>3,47%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>4,58%</t>
+          <t>4,88%</t>
         </is>
       </c>
     </row>
@@ -12562,32 +12562,32 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>117158</t>
+          <t>125278</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>53417</t>
+          <t>105395</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>156550</t>
+          <t>144826</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>9,82%</t>
+          <t>11,94%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>4,48%</t>
+          <t>10,05%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>13,12%</t>
+          <t>13,81%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -12597,32 +12597,32 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>200809</t>
+          <t>224315</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>180999</t>
+          <t>203165</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>220399</t>
+          <t>247464</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>20,96%</t>
+          <t>20,95%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>18,89%</t>
+          <t>18,97%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>23,0%</t>
+          <t>23,11%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -12632,32 +12632,32 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>317967</t>
+          <t>349593</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>210473</t>
+          <t>316743</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>370418</t>
+          <t>380449</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>14,78%</t>
+          <t>16,49%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>9,79%</t>
+          <t>14,94%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>17,22%</t>
+          <t>17,95%</t>
         </is>
       </c>
     </row>
@@ -12675,32 +12675,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>834812</t>
+          <t>679171</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>727826</t>
+          <t>636295</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>1028461</t>
+          <t>713031</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>69,98%</t>
+          <t>64,75%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>61,02%</t>
+          <t>60,66%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>86,22%</t>
+          <t>67,98%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -12710,32 +12710,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>583073</t>
+          <t>649221</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>555704</t>
+          <t>619400</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>607575</t>
+          <t>676292</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>60,86%</t>
+          <t>60,63%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>58,0%</t>
+          <t>57,84%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>63,41%</t>
+          <t>63,16%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -12745,32 +12745,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>1417885</t>
+          <t>1328392</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1307223</t>
+          <t>1283917</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>1665716</t>
+          <t>1376230</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>65,92%</t>
+          <t>62,67%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>60,77%</t>
+          <t>60,57%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>77,44%</t>
+          <t>64,92%</t>
         </is>
       </c>
     </row>
@@ -12788,32 +12788,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>200644</t>
+          <t>200781</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>94075</t>
+          <t>169661</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>270882</t>
+          <t>240429</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>16,82%</t>
+          <t>19,14%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>7,89%</t>
+          <t>16,17%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>22,71%</t>
+          <t>22,92%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -12823,32 +12823,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>109593</t>
+          <t>127031</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>92243</t>
+          <t>105992</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>130711</t>
+          <t>151486</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>11,44%</t>
+          <t>11,86%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>9,63%</t>
+          <t>9,9%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>13,64%</t>
+          <t>14,15%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -12858,32 +12858,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>310237</t>
+          <t>327812</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>202744</t>
+          <t>288209</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>372976</t>
+          <t>370491</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>14,42%</t>
+          <t>15,46%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>9,43%</t>
+          <t>13,6%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>17,34%</t>
+          <t>17,48%</t>
         </is>
       </c>
     </row>
@@ -12901,17 +12901,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>1192864</t>
+          <t>1048917</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>1192864</t>
+          <t>1048917</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>1192864</t>
+          <t>1048917</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -12936,17 +12936,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>958106</t>
+          <t>1070838</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>958106</t>
+          <t>1070838</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>958106</t>
+          <t>1070838</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -12971,17 +12971,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>2150971</t>
+          <t>2119755</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>2150971</t>
+          <t>2119755</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>2150971</t>
+          <t>2119755</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -13018,32 +13018,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>8884</t>
+          <t>9529</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>4003</t>
+          <t>4623</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>16883</t>
+          <t>20063</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>1,26%</t>
+          <t>1,19%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,57%</t>
+          <t>0,58%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>2,4%</t>
+          <t>2,5%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -13053,32 +13053,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>6529</t>
+          <t>8129</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>2076</t>
+          <t>4211</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>12492</t>
+          <t>14919</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0,22%</t>
+          <t>0,52%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>1,34%</t>
+          <t>1,84%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -13088,32 +13088,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>15413</t>
+          <t>17658</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>8396</t>
+          <t>10791</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>25282</t>
+          <t>28030</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>0,94%</t>
+          <t>1,09%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,51%</t>
+          <t>0,67%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>1,54%</t>
+          <t>1,74%</t>
         </is>
       </c>
     </row>
@@ -13131,32 +13131,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>16682</t>
+          <t>18102</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>9830</t>
+          <t>10928</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>25676</t>
+          <t>26803</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>2,37%</t>
+          <t>2,25%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>1,39%</t>
+          <t>1,36%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>3,64%</t>
+          <t>3,34%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -13166,32 +13166,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>30024</t>
+          <t>32764</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>13437</t>
+          <t>24894</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>42896</t>
+          <t>42281</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>3,22%</t>
+          <t>4,03%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>1,44%</t>
+          <t>3,06%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>4,6%</t>
+          <t>5,21%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -13201,32 +13201,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>46706</t>
+          <t>50866</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>30529</t>
+          <t>39447</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>61203</t>
+          <t>62976</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>2,85%</t>
+          <t>3,15%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>1,86%</t>
+          <t>2,44%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>3,74%</t>
+          <t>3,9%</t>
         </is>
       </c>
     </row>
@@ -13244,32 +13244,32 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>104769</t>
+          <t>113733</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>86465</t>
+          <t>95485</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>126405</t>
+          <t>135861</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>14,87%</t>
+          <t>14,16%</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>12,27%</t>
+          <t>11,89%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>17,94%</t>
+          <t>16,92%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -13279,32 +13279,32 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>135838</t>
+          <t>158400</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>63837</t>
+          <t>139386</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>184782</t>
+          <t>178982</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>14,55%</t>
+          <t>19,5%</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>6,84%</t>
+          <t>17,16%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>19,8%</t>
+          <t>22,04%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -13314,32 +13314,32 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>240607</t>
+          <t>272134</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>164653</t>
+          <t>242991</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>287605</t>
+          <t>300035</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
         <is>
-          <t>14,69%</t>
+          <t>16,85%</t>
         </is>
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>10,05%</t>
+          <t>15,04%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>17,56%</t>
+          <t>18,57%</t>
         </is>
       </c>
     </row>
@@ -13357,32 +13357,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>434595</t>
+          <t>497653</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>406240</t>
+          <t>465102</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>463194</t>
+          <t>534891</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>61,67%</t>
+          <t>61,97%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>57,65%</t>
+          <t>57,92%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>65,73%</t>
+          <t>66,61%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -13392,32 +13392,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>641657</t>
+          <t>506404</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>537713</t>
+          <t>480463</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>782789</t>
+          <t>531351</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>68,75%</t>
+          <t>62,35%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>57,61%</t>
+          <t>59,15%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>83,87%</t>
+          <t>65,42%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -13427,32 +13427,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>1076252</t>
+          <t>1004058</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>973250</t>
+          <t>964292</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>1253876</t>
+          <t>1043525</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>65,7%</t>
+          <t>62,16%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>59,42%</t>
+          <t>59,7%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>76,55%</t>
+          <t>64,6%</t>
         </is>
       </c>
     </row>
@@ -13470,32 +13470,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>139750</t>
+          <t>164055</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>114401</t>
+          <t>133263</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>168475</t>
+          <t>195186</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>19,83%</t>
+          <t>20,43%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>16,23%</t>
+          <t>16,59%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>23,91%</t>
+          <t>24,3%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -13505,32 +13505,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>119318</t>
+          <t>106561</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>62369</t>
+          <t>87597</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>223226</t>
+          <t>128863</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>12,78%</t>
+          <t>13,12%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>6,68%</t>
+          <t>10,78%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>23,92%</t>
+          <t>15,86%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -13540,32 +13540,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>259069</t>
+          <t>270617</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>179155</t>
+          <t>238080</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>354812</t>
+          <t>307044</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>15,82%</t>
+          <t>16,75%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>10,94%</t>
+          <t>14,74%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>21,66%</t>
+          <t>19,01%</t>
         </is>
       </c>
     </row>
@@ -13583,17 +13583,17 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>704680</t>
+          <t>803073</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>704680</t>
+          <t>803073</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>704680</t>
+          <t>803073</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -13618,17 +13618,17 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>933366</t>
+          <t>812259</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>933366</t>
+          <t>812259</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>933366</t>
+          <t>812259</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -13653,17 +13653,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>1638046</t>
+          <t>1615332</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>1638046</t>
+          <t>1615332</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>1638046</t>
+          <t>1615332</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -13700,32 +13700,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>10330</t>
+          <t>10671</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>4983</t>
+          <t>5637</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>18200</t>
+          <t>18154</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>1,11%</t>
+          <t>1,08%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>0,54%</t>
+          <t>0,57%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>1,96%</t>
+          <t>1,83%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -13735,32 +13735,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>13369</t>
+          <t>14915</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>8632</t>
+          <t>9695</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>20448</t>
+          <t>22417</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>1,22%</t>
+          <t>1,33%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>0,79%</t>
+          <t>0,87%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>1,87%</t>
+          <t>2,0%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -13770,32 +13770,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>23699</t>
+          <t>25587</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>16188</t>
+          <t>17894</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>34412</t>
+          <t>35395</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>1,17%</t>
+          <t>1,21%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,85%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>1,7%</t>
+          <t>1,68%</t>
         </is>
       </c>
     </row>
@@ -13813,32 +13813,32 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>31818</t>
+          <t>33512</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>22807</t>
+          <t>24710</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>43542</t>
+          <t>46397</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>3,43%</t>
+          <t>3,38%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>2,46%</t>
+          <t>2,5%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>4,7%</t>
+          <t>4,69%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -13848,32 +13848,32 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>54717</t>
+          <t>60558</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>42837</t>
+          <t>49581</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>68479</t>
+          <t>73907</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>5,0%</t>
+          <t>5,41%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>3,91%</t>
+          <t>4,43%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>6,25%</t>
+          <t>6,6%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -13883,32 +13883,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>86535</t>
+          <t>94070</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>71440</t>
+          <t>79605</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>103005</t>
+          <t>109525</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>4,28%</t>
+          <t>4,46%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>3,53%</t>
+          <t>3,77%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>5,09%</t>
+          <t>5,19%</t>
         </is>
       </c>
     </row>
@@ -13926,32 +13926,32 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>140108</t>
+          <t>144833</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>121890</t>
+          <t>123356</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>163288</t>
+          <t>167850</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>15,12%</t>
+          <t>14,63%</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>13,15%</t>
+          <t>12,46%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>17,62%</t>
+          <t>16,95%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -13961,32 +13961,32 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>288514</t>
+          <t>235375</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>225575</t>
+          <t>211608</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>443199</t>
+          <t>261512</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>26,35%</t>
+          <t>21,03%</t>
         </is>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>20,6%</t>
+          <t>18,91%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>40,48%</t>
+          <t>23,37%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -13996,32 +13996,32 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>428622</t>
+          <t>380208</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>360583</t>
+          <t>348784</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>620360</t>
+          <t>412845</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
         <is>
-          <t>21,2%</t>
+          <t>18,03%</t>
         </is>
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>17,84%</t>
+          <t>16,54%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>30,68%</t>
+          <t>19,57%</t>
         </is>
       </c>
     </row>
@@ -14039,32 +14039,32 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>567116</t>
+          <t>613340</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>532916</t>
+          <t>581598</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>599093</t>
+          <t>645804</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>61,19%</t>
+          <t>61,95%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>57,5%</t>
+          <t>58,74%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>64,64%</t>
+          <t>65,23%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -14074,32 +14074,32 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>635689</t>
+          <t>694041</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>510261</t>
+          <t>661005</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>687532</t>
+          <t>719497</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>58,06%</t>
+          <t>62,02%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>46,6%</t>
+          <t>59,07%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>62,79%</t>
+          <t>64,3%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -14109,32 +14109,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>1202805</t>
+          <t>1307382</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>1058553</t>
+          <t>1263091</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>1266123</t>
+          <t>1352107</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>59,49%</t>
+          <t>61,99%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>52,36%</t>
+          <t>59,89%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>62,62%</t>
+          <t>64,11%</t>
         </is>
       </c>
     </row>
@@ -14152,32 +14152,32 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>177460</t>
+          <t>187705</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>149747</t>
+          <t>157753</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>211984</t>
+          <t>219683</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>19,15%</t>
+          <t>18,96%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>16,16%</t>
+          <t>15,93%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>22,87%</t>
+          <t>22,19%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -14187,32 +14187,32 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>102643</t>
+          <t>114152</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>80514</t>
+          <t>96136</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>124811</t>
+          <t>136757</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>9,37%</t>
+          <t>10,2%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>7,35%</t>
+          <t>8,59%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>11,4%</t>
+          <t>12,22%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -14222,32 +14222,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>280103</t>
+          <t>301857</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>237307</t>
+          <t>269100</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>319842</t>
+          <t>340092</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>13,85%</t>
+          <t>14,31%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>11,74%</t>
+          <t>12,76%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>15,82%</t>
+          <t>16,12%</t>
         </is>
       </c>
     </row>
@@ -14265,17 +14265,17 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>926831</t>
+          <t>990062</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>926831</t>
+          <t>990062</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>926831</t>
+          <t>990062</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -14300,17 +14300,17 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>1094932</t>
+          <t>1119041</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>1094932</t>
+          <t>1119041</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>1094932</t>
+          <t>1119041</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -14335,17 +14335,17 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>2021763</t>
+          <t>2109104</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>2021763</t>
+          <t>2109104</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>2021763</t>
+          <t>2109104</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -14382,102 +14382,102 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>36231</t>
+          <t>38527</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>24635</t>
+          <t>27686</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>49269</t>
+          <t>50334</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
+          <t>1,09%</t>
+        </is>
+      </c>
+      <c r="H28" s="2" t="inlineStr">
+        <is>
+          <t>0,78%</t>
+        </is>
+      </c>
+      <c r="I28" s="2" t="inlineStr">
+        <is>
+          <t>1,42%</t>
+        </is>
+      </c>
+      <c r="J28" s="2" t="inlineStr">
+        <is>
+          <t>87</t>
+        </is>
+      </c>
+      <c r="K28" s="2" t="inlineStr">
+        <is>
+          <t>50057</t>
+        </is>
+      </c>
+      <c r="L28" s="2" t="inlineStr">
+        <is>
+          <t>39162</t>
+        </is>
+      </c>
+      <c r="M28" s="2" t="inlineStr">
+        <is>
+          <t>61703</t>
+        </is>
+      </c>
+      <c r="N28" s="2" t="inlineStr">
+        <is>
+          <t>1,34%</t>
+        </is>
+      </c>
+      <c r="O28" s="2" t="inlineStr">
+        <is>
           <t>1,05%</t>
         </is>
       </c>
-      <c r="H28" s="2" t="inlineStr">
-        <is>
-          <t>0,71%</t>
-        </is>
-      </c>
-      <c r="I28" s="2" t="inlineStr">
-        <is>
-          <t>1,42%</t>
-        </is>
-      </c>
-      <c r="J28" s="2" t="inlineStr">
-        <is>
-          <t>87</t>
-        </is>
-      </c>
-      <c r="K28" s="2" t="inlineStr">
-        <is>
-          <t>44518</t>
-        </is>
-      </c>
-      <c r="L28" s="2" t="inlineStr">
-        <is>
-          <t>33979</t>
-        </is>
-      </c>
-      <c r="M28" s="2" t="inlineStr">
-        <is>
-          <t>57409</t>
-        </is>
-      </c>
-      <c r="N28" s="2" t="inlineStr">
+      <c r="P28" s="2" t="inlineStr">
+        <is>
+          <t>1,65%</t>
+        </is>
+      </c>
+      <c r="Q28" s="2" t="inlineStr">
+        <is>
+          <t>131</t>
+        </is>
+      </c>
+      <c r="R28" s="2" t="inlineStr">
+        <is>
+          <t>88584</t>
+        </is>
+      </c>
+      <c r="S28" s="2" t="inlineStr">
+        <is>
+          <t>73250</t>
+        </is>
+      </c>
+      <c r="T28" s="2" t="inlineStr">
+        <is>
+          <t>107021</t>
+        </is>
+      </c>
+      <c r="U28" s="2" t="inlineStr">
         <is>
           <t>1,22%</t>
         </is>
       </c>
-      <c r="O28" s="2" t="inlineStr">
-        <is>
-          <t>0,93%</t>
-        </is>
-      </c>
-      <c r="P28" s="2" t="inlineStr">
-        <is>
-          <t>1,57%</t>
-        </is>
-      </c>
-      <c r="Q28" s="2" t="inlineStr">
-        <is>
-          <t>131</t>
-        </is>
-      </c>
-      <c r="R28" s="2" t="inlineStr">
-        <is>
-          <t>80748</t>
-        </is>
-      </c>
-      <c r="S28" s="2" t="inlineStr">
-        <is>
-          <t>64645</t>
-        </is>
-      </c>
-      <c r="T28" s="2" t="inlineStr">
-        <is>
-          <t>97202</t>
-        </is>
-      </c>
-      <c r="U28" s="2" t="inlineStr">
-        <is>
-          <t>1,13%</t>
-        </is>
-      </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>0,91%</t>
+          <t>1,01%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>1,36%</t>
+          <t>1,47%</t>
         </is>
       </c>
     </row>
@@ -14495,32 +14495,32 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>108497</t>
+          <t>115602</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>80180</t>
+          <t>97545</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>127855</t>
+          <t>136105</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>3,14%</t>
+          <t>3,27%</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>2,32%</t>
+          <t>2,76%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>3,7%</t>
+          <t>3,85%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -14530,32 +14530,32 @@
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>182573</t>
+          <t>198664</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>148327</t>
+          <t>177944</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>206672</t>
+          <t>219673</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>4,99%</t>
+          <t>5,32%</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>4,05%</t>
+          <t>4,76%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>5,64%</t>
+          <t>5,88%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -14565,32 +14565,32 @@
       </c>
       <c r="R29" s="2" t="inlineStr">
         <is>
-          <t>291070</t>
+          <t>314267</t>
         </is>
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>248298</t>
+          <t>287257</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>324741</t>
+          <t>346568</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
         <is>
-          <t>4,09%</t>
+          <t>4,32%</t>
         </is>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>3,49%</t>
+          <t>3,95%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>4,56%</t>
+          <t>4,77%</t>
         </is>
       </c>
     </row>
@@ -14608,32 +14608,32 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>474537</t>
+          <t>504398</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>374703</t>
+          <t>466653</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>530141</t>
+          <t>550041</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>13,72%</t>
+          <t>14,28%</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>10,83%</t>
+          <t>13,21%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>15,32%</t>
+          <t>15,57%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -14643,32 +14643,32 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>776550</t>
+          <t>779889</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>661365</t>
+          <t>738650</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>944665</t>
+          <t>823867</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>21,21%</t>
+          <t>20,88%</t>
         </is>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>18,06%</t>
+          <t>19,78%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>25,8%</t>
+          <t>22,06%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -14678,32 +14678,32 @@
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
-          <t>1251087</t>
+          <t>1284287</t>
         </is>
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>1103574</t>
+          <t>1227681</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>1432343</t>
+          <t>1345532</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
         <is>
-          <t>17,57%</t>
+          <t>17,67%</t>
         </is>
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>15,5%</t>
+          <t>16,89%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>20,11%</t>
+          <t>18,51%</t>
         </is>
       </c>
     </row>
@@ -14721,67 +14721,67 @@
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>2233201</t>
+          <t>2220871</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>2118230</t>
+          <t>2151132</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>2480845</t>
+          <t>2278900</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>64,55%</t>
+          <t>62,86%</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
+          <t>60,89%</t>
+        </is>
+      </c>
+      <c r="I31" s="2" t="inlineStr">
+        <is>
+          <t>64,51%</t>
+        </is>
+      </c>
+      <c r="J31" s="2" t="inlineStr">
+        <is>
+          <t>3180</t>
+        </is>
+      </c>
+      <c r="K31" s="2" t="inlineStr">
+        <is>
+          <t>2286425</t>
+        </is>
+      </c>
+      <c r="L31" s="2" t="inlineStr">
+        <is>
+          <t>2234257</t>
+        </is>
+      </c>
+      <c r="M31" s="2" t="inlineStr">
+        <is>
+          <t>2340617</t>
+        </is>
+      </c>
+      <c r="N31" s="2" t="inlineStr">
+        <is>
           <t>61,22%</t>
         </is>
       </c>
-      <c r="I31" s="2" t="inlineStr">
-        <is>
-          <t>71,7%</t>
-        </is>
-      </c>
-      <c r="J31" s="2" t="inlineStr">
-        <is>
-          <t>3180</t>
-        </is>
-      </c>
-      <c r="K31" s="2" t="inlineStr">
-        <is>
-          <t>2263373</t>
-        </is>
-      </c>
-      <c r="L31" s="2" t="inlineStr">
-        <is>
-          <t>2131766</t>
-        </is>
-      </c>
-      <c r="M31" s="2" t="inlineStr">
-        <is>
-          <t>2522759</t>
-        </is>
-      </c>
-      <c r="N31" s="2" t="inlineStr">
-        <is>
-          <t>61,81%</t>
-        </is>
-      </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>58,22%</t>
+          <t>59,82%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>68,89%</t>
+          <t>62,67%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -14791,32 +14791,32 @@
       </c>
       <c r="R31" s="2" t="inlineStr">
         <is>
-          <t>4496574</t>
+          <t>4507296</t>
         </is>
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>4292537</t>
+          <t>4427634</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>4842420</t>
+          <t>4591198</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
         <is>
-          <t>63,14%</t>
+          <t>62,02%</t>
         </is>
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>60,27%</t>
+          <t>60,92%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>68,0%</t>
+          <t>63,17%</t>
         </is>
       </c>
     </row>
@@ -14834,32 +14834,32 @@
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>607351</t>
+          <t>653364</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>481348</t>
+          <t>596357</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>681371</t>
+          <t>717222</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>17,55%</t>
+          <t>18,49%</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>13,91%</t>
+          <t>16,88%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>19,69%</t>
+          <t>20,3%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -14869,32 +14869,32 @@
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>394761</t>
+          <t>419825</t>
         </is>
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>325551</t>
+          <t>385555</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>487948</t>
+          <t>462032</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
         <is>
-          <t>10,78%</t>
+          <t>11,24%</t>
         </is>
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>8,89%</t>
+          <t>10,32%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>13,33%</t>
+          <t>12,37%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -14904,32 +14904,32 @@
       </c>
       <c r="R32" s="2" t="inlineStr">
         <is>
-          <t>1002112</t>
+          <t>1073189</t>
         </is>
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>860064</t>
+          <t>1001985</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>1116236</t>
+          <t>1144725</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
         <is>
-          <t>14,07%</t>
+          <t>14,77%</t>
         </is>
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>12,08%</t>
+          <t>13,79%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>15,67%</t>
+          <t>15,75%</t>
         </is>
       </c>
     </row>
@@ -14947,17 +14947,17 @@
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>3459817</t>
+          <t>3532762</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>3459817</t>
+          <t>3532762</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>3459817</t>
+          <t>3532762</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -14982,17 +14982,17 @@
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>3661774</t>
+          <t>3734860</t>
         </is>
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>3661774</t>
+          <t>3734860</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>3661774</t>
+          <t>3734860</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -15017,17 +15017,17 @@
       </c>
       <c r="R33" s="2" t="inlineStr">
         <is>
-          <t>7121591</t>
+          <t>7267622</t>
         </is>
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>7121591</t>
+          <t>7267622</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>7121591</t>
+          <t>7267622</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
